--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$105</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4031" uniqueCount="701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4228" uniqueCount="724">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1075,6 +1075,9 @@
     <t>.role</t>
   </si>
   <si>
+    <t>1715: reference from PRESCRIPTION - REFILL &gt; REFILL - DIVISION (#52-52 &gt; 52.1-8)</t>
+  </si>
+  <si>
     <t>MedicationDispense.location</t>
   </si>
   <si>
@@ -1153,6 +1156,9 @@
   </si>
   <si>
     <t>RXD-33-Dispense Type</t>
+  </si>
+  <si>
+    <t>1709: fixed value = RF</t>
   </si>
   <si>
     <t>MedicationDispense.quantity</t>
@@ -1527,6 +1533,71 @@
   </si>
   <si>
     <t>RXD-9 Dispense Notes</t>
+  </si>
+  <si>
+    <t>MedicationDispense.note.id</t>
+  </si>
+  <si>
+    <t>MedicationDispense.note.extension</t>
+  </si>
+  <si>
+    <t>MedicationDispense.note.author[x]</t>
+  </si>
+  <si>
+    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+string</t>
+  </si>
+  <si>
+    <t>Individual responsible for the annotation</t>
+  </si>
+  <si>
+    <t>The individual responsible for making the annotation.</t>
+  </si>
+  <si>
+    <t>Organization is used when there's no need for specific attribution as to who made the comment.</t>
+  </si>
+  <si>
+    <t>Annotation.author[x]</t>
+  </si>
+  <si>
+    <t>Act.participant[typeCode=AUT].role</t>
+  </si>
+  <si>
+    <t>MedicationDispense.note.time</t>
+  </si>
+  <si>
+    <t>When the annotation was made</t>
+  </si>
+  <si>
+    <t>Indicates when this particular annotation was made.</t>
+  </si>
+  <si>
+    <t>Annotation.time</t>
+  </si>
+  <si>
+    <t>Act.effectiveTime</t>
+  </si>
+  <si>
+    <t>MedicationDispense.note.text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">markdown
+</t>
+  </si>
+  <si>
+    <t>The annotation  - text content (as markdown)</t>
+  </si>
+  <si>
+    <t>The text of the annotation in markdown format.</t>
+  </si>
+  <si>
+    <t>Annotation.text</t>
+  </si>
+  <si>
+    <t>Act.text</t>
+  </si>
+  <si>
+    <t>1718: source value from PRESCRIPTION - REFILL &gt; REFILL - REMARKS (#52-52 &gt; 52.1-3)</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction</t>
@@ -2508,7 +2579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR100"/>
+  <dimension ref="A1:AR105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="80.94140625" customWidth="true" bestFit="true"/>
@@ -7111,7 +7182,7 @@
         <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>81</v>
@@ -7207,7 +7278,7 @@
         <v>81</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -7218,10 +7289,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7244,13 +7315,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7301,7 +7372,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7319,7 +7390,7 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
@@ -7331,21 +7402,21 @@
         <v>81</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7368,16 +7439,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7427,7 +7498,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7442,25 +7513,25 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>81</v>
@@ -7468,10 +7539,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7485,7 +7556,7 @@
         <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>81</v>
@@ -7497,10 +7568,10 @@
         <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7530,10 +7601,10 @@
         <v>179</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -7551,7 +7622,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7569,19 +7640,19 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>81</v>
@@ -7592,10 +7663,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7618,13 +7689,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7675,7 +7746,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7693,16 +7764,16 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
@@ -7716,10 +7787,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7840,10 +7911,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7966,10 +8037,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7992,19 +8063,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8053,7 +8124,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8071,7 +8142,7 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
@@ -8080,24 +8151,24 @@
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8123,20 +8194,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8160,10 +8231,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8181,7 +8252,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8199,7 +8270,7 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -8208,7 +8279,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8222,10 +8293,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8251,14 +8322,14 @@
         <v>210</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8307,7 +8378,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8325,7 +8396,7 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -8334,7 +8405,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8348,10 +8419,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8377,14 +8448,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8433,7 +8504,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8442,7 +8513,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8451,7 +8522,7 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -8460,7 +8531,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8474,10 +8545,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8503,16 +8574,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8561,7 +8632,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8579,7 +8650,7 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
@@ -8588,7 +8659,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8602,10 +8673,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8628,13 +8699,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8685,7 +8756,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8703,7 +8774,7 @@
         <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
@@ -8712,24 +8783,24 @@
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8752,13 +8823,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8809,7 +8880,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8827,19 +8898,19 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>81</v>
@@ -8850,10 +8921,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8876,13 +8947,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8933,7 +9004,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8948,22 +9019,22 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>81</v>
@@ -8974,10 +9045,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9000,13 +9071,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9057,7 +9128,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9075,16 +9146,16 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
@@ -9098,10 +9169,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9222,10 +9293,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9348,10 +9419,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9377,13 +9448,13 @@
         <v>210</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9433,7 +9504,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9442,7 +9513,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9474,10 +9545,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9503,13 +9574,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9535,13 +9606,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9559,7 +9630,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9600,10 +9671,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9629,13 +9700,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9685,7 +9756,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9703,7 +9774,7 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
@@ -9726,10 +9797,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9755,13 +9826,13 @@
         <v>210</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9811,7 +9882,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9841,21 +9912,21 @@
         <v>81</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9878,13 +9949,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9935,7 +10006,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9953,13 +10024,13 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -9976,10 +10047,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10002,13 +10073,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10059,7 +10130,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10074,10 +10145,10 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
@@ -10086,7 +10157,7 @@
         <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10100,10 +10171,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10114,7 +10185,7 @@
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
@@ -10126,17 +10197,15 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>486</v>
+        <v>210</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>487</v>
+        <v>211</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>489</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -10185,25 +10254,25 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>485</v>
+        <v>213</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>490</v>
+        <v>214</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
@@ -10226,21 +10295,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -10252,15 +10321,17 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>210</v>
+        <v>137</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>211</v>
+        <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -10297,31 +10368,31 @@
         <v>81</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>81</v>
+        <v>218</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>81</v>
+        <v>219</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>81</v>
@@ -10350,21 +10421,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -10373,19 +10444,19 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>137</v>
+        <v>490</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>138</v>
+        <v>491</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>217</v>
+        <v>492</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>140</v>
+        <v>493</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10423,37 +10494,37 @@
         <v>81</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>219</v>
+        <v>81</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>220</v>
+        <v>494</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>214</v>
+        <v>495</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
@@ -10462,7 +10533,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10476,46 +10547,42 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>322</v>
+        <v>81</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>137</v>
+        <v>426</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>323</v>
+        <v>497</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
       </c>
@@ -10563,34 +10630,34 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>325</v>
+        <v>499</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10604,10 +10671,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10615,13 +10682,13 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>81</v>
@@ -10630,18 +10697,16 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>498</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>81</v>
       </c>
@@ -10689,10 +10754,10 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>91</v>
@@ -10707,7 +10772,7 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
@@ -10716,10 +10781,10 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>501</v>
+        <v>134</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>81</v>
+        <v>507</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>81</v>
@@ -10730,10 +10795,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10744,30 +10809,30 @@
         <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>210</v>
+        <v>509</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
@@ -10815,13 +10880,13 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
@@ -10833,7 +10898,7 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -10842,24 +10907,24 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>507</v>
+        <v>81</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>508</v>
+        <v>81</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>509</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10870,7 +10935,7 @@
         <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>81</v>
@@ -10879,23 +10944,19 @@
         <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>511</v>
+        <v>211</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>514</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
@@ -10919,13 +10980,13 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>515</v>
+        <v>81</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>516</v>
+        <v>81</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -10943,25 +11004,25 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>517</v>
+        <v>213</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>500</v>
+        <v>214</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
@@ -10970,7 +11031,7 @@
         <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>518</v>
+        <v>81</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>81</v>
@@ -10984,41 +11045,43 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>210</v>
+        <v>137</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>520</v>
+        <v>138</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -11055,37 +11118,37 @@
         <v>81</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>81</v>
+        <v>218</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>81</v>
+        <v>219</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>522</v>
+        <v>220</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>500</v>
+        <v>214</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
@@ -11094,13 +11157,13 @@
         <v>81</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>518</v>
+        <v>81</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>523</v>
+        <v>81</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>524</v>
+        <v>81</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>81</v>
@@ -11108,45 +11171,45 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>81</v>
+        <v>322</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>526</v>
+        <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>527</v>
+        <v>323</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>528</v>
+        <v>324</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>529</v>
+        <v>140</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>530</v>
+        <v>146</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -11195,25 +11258,25 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>531</v>
+        <v>325</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>532</v>
+        <v>134</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>81</v>
@@ -11236,10 +11299,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11262,18 +11325,18 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>520</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
       </c>
@@ -11297,13 +11360,13 @@
         <v>81</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>538</v>
+        <v>81</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>539</v>
+        <v>81</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>81</v>
@@ -11321,7 +11384,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11339,7 +11402,7 @@
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>81</v>
@@ -11348,7 +11411,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11362,10 +11425,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11379,7 +11442,7 @@
         <v>91</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>81</v>
@@ -11388,19 +11451,17 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>546</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>547</v>
+        <v>528</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11425,13 +11486,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>548</v>
+        <v>81</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>549</v>
+        <v>81</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -11449,7 +11510,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>550</v>
+        <v>529</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11467,7 +11528,7 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>551</v>
+        <v>523</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -11476,24 +11537,24 @@
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>552</v>
+        <v>530</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>81</v>
+        <v>531</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11504,7 +11565,7 @@
         <v>82</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>81</v>
@@ -11519,14 +11580,16 @@
         <v>185</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="O72" t="s" s="2">
-        <v>556</v>
+        <v>537</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11554,10 +11617,10 @@
         <v>179</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>557</v>
+        <v>538</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>558</v>
+        <v>539</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11575,13 +11638,13 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>559</v>
+        <v>540</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>81</v>
@@ -11593,7 +11656,7 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>560</v>
+        <v>523</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
@@ -11602,7 +11665,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>561</v>
+        <v>541</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11616,10 +11679,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11633,7 +11696,7 @@
         <v>91</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>81</v>
@@ -11642,20 +11705,16 @@
         <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>566</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>81</v>
       </c>
@@ -11679,13 +11738,13 @@
         <v>81</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>81</v>
@@ -11703,7 +11762,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11721,7 +11780,7 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>570</v>
+        <v>523</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11730,13 +11789,13 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>571</v>
+        <v>541</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>81</v>
+        <v>546</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>81</v>
+        <v>547</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>81</v>
@@ -11744,10 +11803,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>572</v>
+        <v>548</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>572</v>
+        <v>548</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11758,7 +11817,7 @@
         <v>82</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
@@ -11770,16 +11829,20 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>573</v>
+        <v>549</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>574</v>
+        <v>550</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
@@ -11827,13 +11890,13 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>576</v>
+        <v>554</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>81</v>
@@ -11845,7 +11908,7 @@
         <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>81</v>
+        <v>555</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
@@ -11854,7 +11917,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>577</v>
+        <v>81</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11868,10 +11931,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11891,18 +11954,20 @@
         <v>81</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>210</v>
+        <v>557</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>211</v>
+        <v>558</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>559</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -11927,13 +11992,13 @@
         <v>81</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>81</v>
+        <v>561</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>81</v>
+        <v>562</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -11951,7 +12016,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>213</v>
+        <v>563</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11963,13 +12028,13 @@
         <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>214</v>
+        <v>564</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
@@ -11978,7 +12043,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>81</v>
+        <v>565</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -11992,21 +12057,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>81</v>
@@ -12015,21 +12080,23 @@
         <v>81</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>138</v>
+        <v>567</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>217</v>
+        <v>568</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>569</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>570</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
@@ -12053,49 +12120,49 @@
         <v>81</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>81</v>
+        <v>571</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>81</v>
+        <v>572</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>219</v>
+        <v>81</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>220</v>
+        <v>573</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>214</v>
+        <v>574</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
@@ -12104,7 +12171,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>81</v>
+        <v>575</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12118,10 +12185,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12147,14 +12214,14 @@
         <v>185</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12182,10 +12249,10 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12203,7 +12270,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12221,7 +12288,7 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>81</v>
+        <v>583</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>81</v>
@@ -12230,7 +12297,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12244,10 +12311,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12270,19 +12337,19 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="O78" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12307,29 +12374,31 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>81</v>
+        <v>590</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>81</v>
+        <v>591</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AC78" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12347,7 +12416,7 @@
         <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>570</v>
+        <v>593</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>81</v>
@@ -12356,7 +12425,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12370,14 +12439,12 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>81</v>
       </c>
@@ -12386,7 +12453,7 @@
         <v>82</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>81</v>
@@ -12395,23 +12462,19 @@
         <v>81</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>366</v>
+        <v>596</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="M79" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>593</v>
-      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>81</v>
       </c>
@@ -12459,25 +12522,25 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>601</v>
+        <v>81</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>602</v>
+        <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>603</v>
+        <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>81</v>
@@ -12486,7 +12549,7 @@
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>81</v>
@@ -12500,10 +12563,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12624,10 +12687,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12750,10 +12813,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12767,7 +12830,7 @@
         <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>81</v>
@@ -12776,19 +12839,17 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>375</v>
+        <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>376</v>
+        <v>604</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>379</v>
+        <v>606</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12813,13 +12874,13 @@
         <v>81</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>81</v>
+        <v>607</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>81</v>
+        <v>608</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12837,7 +12898,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>380</v>
+        <v>609</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12855,7 +12916,7 @@
         <v>81</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>81</v>
@@ -12864,24 +12925,24 @@
         <v>81</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>382</v>
+        <v>610</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>611</v>
+        <v>81</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>612</v>
+        <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>613</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12892,36 +12953,36 @@
         <v>82</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>111</v>
+        <v>612</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>386</v>
+        <v>613</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>614</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="O83" t="s" s="2">
-        <v>388</v>
+        <v>616</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q83" t="s" s="2">
-        <v>389</v>
-      </c>
+      <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
         <v>81</v>
       </c>
@@ -12941,31 +13002,29 @@
         <v>81</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>391</v>
+        <v>81</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>392</v>
+        <v>617</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -12983,7 +13042,7 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>393</v>
+        <v>593</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>81</v>
@@ -12992,7 +13051,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>394</v>
+        <v>618</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13006,12 +13065,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="C84" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>620</v>
+      </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
       </c>
@@ -13023,26 +13084,28 @@
         <v>91</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>210</v>
+        <v>368</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>396</v>
+        <v>621</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>622</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="O84" t="s" s="2">
-        <v>398</v>
+        <v>616</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13091,7 +13154,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>399</v>
+        <v>617</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13100,16 +13163,16 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>81</v>
+        <v>624</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>103</v>
+        <v>625</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>400</v>
+        <v>626</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
@@ -13118,24 +13181,24 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>401</v>
+        <v>627</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>618</v>
+        <v>81</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>619</v>
+        <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>620</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13155,21 +13218,19 @@
         <v>81</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>105</v>
+        <v>210</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>403</v>
+        <v>211</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>404</v>
+        <v>212</v>
       </c>
       <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>405</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>81</v>
       </c>
@@ -13217,7 +13278,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>406</v>
+        <v>213</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13226,16 +13287,16 @@
         <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>408</v>
+        <v>214</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
@@ -13244,7 +13305,7 @@
         <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>401</v>
+        <v>81</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>81</v>
@@ -13258,46 +13319,44 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>410</v>
+        <v>138</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>411</v>
+        <v>217</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>81</v>
       </c>
@@ -13333,37 +13392,37 @@
         <v>81</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>81</v>
+        <v>218</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>81</v>
+        <v>219</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>414</v>
+        <v>220</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>415</v>
+        <v>214</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
@@ -13372,24 +13431,24 @@
         <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>401</v>
+        <v>81</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>625</v>
+        <v>81</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>619</v>
+        <v>81</v>
       </c>
       <c r="AR86" t="s" s="2">
-        <v>620</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13403,7 +13462,7 @@
         <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>81</v>
@@ -13412,19 +13471,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>627</v>
+        <v>377</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>628</v>
+        <v>378</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>629</v>
+        <v>379</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>630</v>
+        <v>380</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>631</v>
+        <v>381</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13473,7 +13532,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>632</v>
+        <v>382</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13491,7 +13550,7 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>633</v>
+        <v>383</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
@@ -13500,24 +13559,24 @@
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AP87" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="AP87" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AQ87" t="s" s="2">
-        <v>81</v>
+        <v>635</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>81</v>
+        <v>636</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13528,36 +13587,36 @@
         <v>82</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J88" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>636</v>
+        <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>637</v>
+        <v>388</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>639</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>640</v>
+        <v>390</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q88" s="2"/>
+      <c r="Q88" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
       </c>
@@ -13577,13 +13636,13 @@
         <v>81</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>81</v>
+        <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>81</v>
+        <v>393</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13601,7 +13660,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>641</v>
+        <v>394</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13619,7 +13678,7 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>642</v>
+        <v>395</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>81</v>
@@ -13628,7 +13687,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>643</v>
+        <v>396</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13642,10 +13701,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13659,7 +13718,7 @@
         <v>91</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>81</v>
@@ -13668,19 +13727,17 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>366</v>
+        <v>210</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>645</v>
+        <v>398</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>647</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>648</v>
+        <v>400</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13729,7 +13786,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>649</v>
+        <v>401</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13747,7 +13804,7 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>650</v>
+        <v>402</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
@@ -13756,24 +13813,24 @@
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>81</v>
+        <v>641</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>81</v>
+        <v>642</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>81</v>
+        <v>643</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13796,17 +13853,17 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>366</v>
+        <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>652</v>
+        <v>405</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>653</v>
+        <v>406</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>654</v>
+        <v>407</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13855,7 +13912,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>655</v>
+        <v>408</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13864,7 +13921,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13873,7 +13930,7 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>650</v>
+        <v>410</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
@@ -13882,7 +13939,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13896,10 +13953,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13913,25 +13970,29 @@
         <v>91</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>314</v>
+        <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>657</v>
+        <v>412</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
       </c>
@@ -13979,7 +14040,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>656</v>
+        <v>416</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -13997,33 +14058,33 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>659</v>
+        <v>417</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>660</v>
+        <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>81</v>
+        <v>648</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>81</v>
+        <v>642</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>81</v>
+        <v>643</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14043,19 +14104,23 @@
         <v>81</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>210</v>
+        <v>650</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>211</v>
+        <v>651</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+        <v>652</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>654</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
       </c>
@@ -14103,7 +14168,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>213</v>
+        <v>655</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14115,13 +14180,13 @@
         <v>81</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>214</v>
+        <v>656</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>81</v>
@@ -14130,7 +14195,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>81</v>
+        <v>657</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14144,21 +14209,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>81</v>
@@ -14167,21 +14232,23 @@
         <v>81</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>137</v>
+        <v>659</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>138</v>
+        <v>660</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>217</v>
+        <v>661</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>662</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>663</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
       </c>
@@ -14229,25 +14296,25 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>220</v>
+        <v>664</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>214</v>
+        <v>665</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>81</v>
@@ -14256,7 +14323,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>81</v>
+        <v>666</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14270,45 +14337,45 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>322</v>
+        <v>81</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>137</v>
+        <v>368</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>323</v>
+        <v>668</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>324</v>
+        <v>669</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>140</v>
+        <v>670</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>146</v>
+        <v>671</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14357,25 +14424,25 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>325</v>
+        <v>672</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>134</v>
+        <v>673</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>81</v>
@@ -14398,10 +14465,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>664</v>
+        <v>674</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>664</v>
+        <v>674</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14409,7 +14476,7 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>91</v>
@@ -14421,19 +14488,21 @@
         <v>81</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>272</v>
+        <v>368</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>677</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
       </c>
@@ -14481,10 +14550,10 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>664</v>
+        <v>678</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>91</v>
@@ -14499,7 +14568,7 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
@@ -14522,10 +14591,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14548,13 +14617,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>185</v>
+        <v>314</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>670</v>
+        <v>681</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14581,13 +14650,13 @@
         <v>81</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>671</v>
+        <v>81</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>672</v>
+        <v>81</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -14605,7 +14674,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14623,16 +14692,16 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>362</v>
+        <v>682</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>674</v>
+        <v>81</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
@@ -14646,10 +14715,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14660,7 +14729,7 @@
         <v>82</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>81</v>
@@ -14672,13 +14741,13 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>676</v>
+        <v>211</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>677</v>
+        <v>212</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14705,13 +14774,13 @@
         <v>81</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>678</v>
+        <v>81</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>679</v>
+        <v>81</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -14729,31 +14798,31 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>675</v>
+        <v>213</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>680</v>
+        <v>214</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>681</v>
+        <v>81</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>81</v>
@@ -14770,14 +14839,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14796,15 +14865,17 @@
         <v>81</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>683</v>
+        <v>137</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>684</v>
+        <v>138</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -14853,7 +14924,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>682</v>
+        <v>220</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -14865,19 +14936,19 @@
         <v>81</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>686</v>
+        <v>214</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>687</v>
+        <v>81</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>81</v>
@@ -14894,14 +14965,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>689</v>
+        <v>322</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14914,24 +14985,26 @@
         <v>81</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>690</v>
+        <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>691</v>
+        <v>323</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>692</v>
+        <v>324</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
       </c>
@@ -14979,7 +15052,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>688</v>
+        <v>325</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -14991,13 +15064,13 @@
         <v>81</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>694</v>
+        <v>134</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
@@ -15020,10 +15093,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15031,10 +15104,10 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>81</v>
@@ -15046,17 +15119,15 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>696</v>
+        <v>272</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>699</v>
-      </c>
+        <v>689</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>81</v>
@@ -15105,13 +15176,13 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>81</v>
@@ -15123,29 +15194,653 @@
         <v>81</v>
       </c>
       <c r="AL100" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR100" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR101" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="AM100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR100" t="s" s="2">
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR102" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR103" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR104" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR105" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR100">
+  <autoFilter ref="A1:AR105">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15155,7 +15850,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI99">
+  <conditionalFormatting sqref="A2:AI104">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4228" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="725">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2029,7 +2029,10 @@
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].code</t>
   </si>
   <si>
-    <t>1579: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (#52-113 &gt; 52.0113-2)</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFDoseUnits</t>
+  </si>
+  <si>
+    <t>1579: terminologyMaps using VF_DoseUnits on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (#52-113 &gt; 52.0113-2)</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.rate[x]</t>
@@ -14016,13 +14019,11 @@
         <v>81</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>81</v>
+        <v>648</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14070,7 +14071,7 @@
         <v>403</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>642</v>
@@ -14081,10 +14082,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14107,19 +14108,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14168,7 +14169,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14186,7 +14187,7 @@
         <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>81</v>
@@ -14195,7 +14196,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14209,10 +14210,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14235,19 +14236,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14296,7 +14297,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14314,7 +14315,7 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>81</v>
@@ -14323,7 +14324,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14337,10 +14338,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14366,16 +14367,16 @@
         <v>368</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14424,7 +14425,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14442,7 +14443,7 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>81</v>
@@ -14465,10 +14466,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14494,14 +14495,14 @@
         <v>368</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14550,7 +14551,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14568,7 +14569,7 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
@@ -14591,10 +14592,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14620,10 +14621,10 @@
         <v>314</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14674,7 +14675,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14692,13 +14693,13 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>81</v>
@@ -14715,10 +14716,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14839,10 +14840,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14965,10 +14966,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15093,10 +15094,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15122,10 +15123,10 @@
         <v>272</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15176,7 +15177,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15194,7 +15195,7 @@
         <v>81</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>
@@ -15217,10 +15218,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15246,10 +15247,10 @@
         <v>185</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15279,10 +15280,10 @@
         <v>179</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15300,7 +15301,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15324,10 +15325,10 @@
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
@@ -15341,10 +15342,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15370,10 +15371,10 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15403,10 +15404,10 @@
         <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15424,7 +15425,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15442,13 +15443,13 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -15465,10 +15466,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15491,13 +15492,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15548,7 +15549,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15566,13 +15567,13 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -15589,14 +15590,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15615,16 +15616,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15674,7 +15675,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15692,7 +15693,7 @@
         <v>81</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>81</v>
@@ -15715,10 +15716,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15741,16 +15742,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15800,7 +15801,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15818,7 +15819,7 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="726">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -557,7 +557,7 @@
     <t>CombinedMedicationDispense.SupplyEvent.statusCode</t>
   </si>
   <si>
-    <t>1555: fixed value = in-progress when PRESCRIPTION - RELEASED DATE/TIME (#52-31) case null</t>
+    <t>1555: fixed value = #in-progress when PRESCRIPTION - RELEASED DATE/TIME (#52-31) case null</t>
   </si>
   <si>
     <t>MedicationDispense.statusReason[x]</t>
@@ -1146,6 +1146,13 @@
     <t>Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="RF"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType</t>
   </si>
   <si>
@@ -1158,7 +1165,7 @@
     <t>RXD-33-Dispense Type</t>
   </si>
   <si>
-    <t>1709: fixed value = RF</t>
+    <t>1709: fixed value = #RF</t>
   </si>
   <si>
     <t>MedicationDispense.quantity</t>
@@ -7586,7 +7593,7 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>81</v>
@@ -7607,7 +7614,7 @@
         <v>361</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -7643,19 +7650,19 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>81</v>
@@ -7666,10 +7673,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7692,13 +7699,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7749,7 +7756,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7767,16 +7774,16 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
@@ -7790,10 +7797,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7914,10 +7921,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8040,10 +8047,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8066,19 +8073,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8127,7 +8134,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8145,7 +8152,7 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
@@ -8154,24 +8161,24 @@
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8197,20 +8204,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8234,10 +8241,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8255,7 +8262,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8273,7 +8280,7 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -8282,7 +8289,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8296,10 +8303,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8325,14 +8332,14 @@
         <v>210</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8381,7 +8388,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8399,7 +8406,7 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -8408,7 +8415,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8422,10 +8429,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8451,14 +8458,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8507,7 +8514,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8516,7 +8523,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8525,7 +8532,7 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -8534,7 +8541,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8548,10 +8555,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8577,16 +8584,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8635,7 +8642,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8653,7 +8660,7 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
@@ -8662,7 +8669,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8676,10 +8683,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8702,13 +8709,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8759,7 +8766,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8777,7 +8784,7 @@
         <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
@@ -8786,24 +8793,24 @@
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8826,13 +8833,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8883,7 +8890,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8901,19 +8908,19 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>81</v>
@@ -8924,10 +8931,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8950,13 +8957,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9007,7 +9014,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9022,22 +9029,22 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>81</v>
@@ -9048,10 +9055,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9077,10 +9084,10 @@
         <v>341</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9131,7 +9138,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9149,16 +9156,16 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
@@ -9172,10 +9179,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9296,10 +9303,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9422,10 +9429,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9451,13 +9458,13 @@
         <v>210</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9507,7 +9514,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9516,7 +9523,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9548,10 +9555,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9577,13 +9584,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9609,13 +9616,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9633,7 +9640,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9674,10 +9681,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9703,13 +9710,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9759,7 +9766,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9777,7 +9784,7 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
@@ -9800,10 +9807,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9829,13 +9836,13 @@
         <v>210</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9885,7 +9892,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9915,21 +9922,21 @@
         <v>81</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9952,13 +9959,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10009,7 +10016,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10027,13 +10034,13 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -10050,10 +10057,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10076,13 +10083,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10133,7 +10140,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10148,10 +10155,10 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
@@ -10160,7 +10167,7 @@
         <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10174,10 +10181,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10298,10 +10305,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10424,10 +10431,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10450,16 +10457,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10509,7 +10516,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10527,7 +10534,7 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
@@ -10550,10 +10557,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10576,13 +10583,13 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10633,7 +10640,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10651,7 +10658,7 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
@@ -10674,10 +10681,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10700,13 +10707,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10757,7 +10764,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10775,7 +10782,7 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
@@ -10787,7 +10794,7 @@
         <v>134</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>81</v>
@@ -10798,10 +10805,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10824,16 +10831,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10883,7 +10890,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10901,7 +10908,7 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -10924,10 +10931,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11048,10 +11055,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11174,10 +11181,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11302,10 +11309,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11328,17 +11335,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11387,7 +11394,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11405,7 +11412,7 @@
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>81</v>
@@ -11414,7 +11421,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11428,10 +11435,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11457,14 +11464,14 @@
         <v>210</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11513,7 +11520,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11531,7 +11538,7 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -11540,24 +11547,24 @@
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11583,16 +11590,16 @@
         <v>185</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11620,10 +11627,10 @@
         <v>179</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11641,7 +11648,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11659,7 +11666,7 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
@@ -11668,7 +11675,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11682,10 +11689,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11711,10 +11718,10 @@
         <v>210</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11765,7 +11772,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11783,7 +11790,7 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11792,13 +11799,13 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>81</v>
@@ -11806,10 +11813,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11832,19 +11839,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11893,7 +11900,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11911,7 +11918,7 @@
         <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
@@ -11934,10 +11941,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11960,16 +11967,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11998,10 +12005,10 @@
         <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12019,7 +12026,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12037,7 +12044,7 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
@@ -12046,7 +12053,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12060,10 +12067,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12089,16 +12096,16 @@
         <v>185</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12126,10 +12133,10 @@
         <v>179</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12147,7 +12154,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12165,7 +12172,7 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
@@ -12174,7 +12181,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12188,10 +12195,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12217,14 +12224,14 @@
         <v>185</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12252,10 +12259,10 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12273,7 +12280,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12291,7 +12298,7 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>81</v>
@@ -12300,7 +12307,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12314,10 +12321,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12343,16 +12350,16 @@
         <v>185</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12380,10 +12387,10 @@
         <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12401,7 +12408,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12419,7 +12426,7 @@
         <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>81</v>
@@ -12428,7 +12435,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12442,10 +12449,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12468,13 +12475,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12525,7 +12532,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12552,7 +12559,7 @@
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>81</v>
@@ -12566,10 +12573,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12690,10 +12697,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12816,10 +12823,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12845,14 +12852,14 @@
         <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12880,10 +12887,10 @@
         <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12901,7 +12908,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12928,7 +12935,7 @@
         <v>81</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>81</v>
@@ -12942,10 +12949,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12968,19 +12975,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13027,7 +13034,7 @@
         <v>200</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13045,7 +13052,7 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>81</v>
@@ -13054,7 +13061,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13068,13 +13075,13 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13096,19 +13103,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13157,7 +13164,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13166,16 +13173,16 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
@@ -13184,7 +13191,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13198,10 +13205,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13322,10 +13329,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13448,10 +13455,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13474,19 +13481,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13535,7 +13542,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13553,7 +13560,7 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
@@ -13562,24 +13569,24 @@
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13605,20 +13612,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13642,10 +13649,10 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13663,7 +13670,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13681,7 +13688,7 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>81</v>
@@ -13690,7 +13697,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13704,10 +13711,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13733,14 +13740,14 @@
         <v>210</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13789,7 +13796,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13807,7 +13814,7 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
@@ -13816,24 +13823,24 @@
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13859,14 +13866,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13915,7 +13922,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13924,7 +13931,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13933,7 +13940,7 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
@@ -13942,7 +13949,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13956,10 +13963,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13985,16 +13992,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14023,7 +14030,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14041,7 +14048,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14059,7 +14066,7 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
@@ -14068,24 +14075,24 @@
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14108,19 +14115,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14169,7 +14176,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14187,7 +14194,7 @@
         <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>81</v>
@@ -14196,7 +14203,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14210,10 +14217,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14236,19 +14243,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14297,7 +14304,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14315,7 +14322,7 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>81</v>
@@ -14324,7 +14331,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14338,10 +14345,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14364,19 +14371,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14425,7 +14432,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14443,7 +14450,7 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>81</v>
@@ -14466,10 +14473,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14492,17 +14499,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14551,7 +14558,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14569,7 +14576,7 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
@@ -14592,10 +14599,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14621,10 +14628,10 @@
         <v>314</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14675,7 +14682,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14693,13 +14700,13 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>81</v>
@@ -14716,10 +14723,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14840,10 +14847,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14966,10 +14973,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15094,10 +15101,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15123,10 +15130,10 @@
         <v>272</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15177,7 +15184,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15195,7 +15202,7 @@
         <v>81</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>
@@ -15218,10 +15225,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15247,10 +15254,10 @@
         <v>185</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15280,10 +15287,10 @@
         <v>179</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15301,7 +15308,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15319,16 +15326,16 @@
         <v>81</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
@@ -15342,10 +15349,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15371,10 +15378,10 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15404,10 +15411,10 @@
         <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15425,7 +15432,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15443,13 +15450,13 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -15466,10 +15473,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15492,13 +15499,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15549,7 +15556,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15567,13 +15574,13 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -15590,14 +15597,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15616,16 +15623,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15675,7 +15682,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15693,7 +15700,7 @@
         <v>81</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>81</v>
@@ -15716,10 +15723,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15742,16 +15749,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15801,7 +15808,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15819,7 +15826,7 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -825,9 +825,7 @@
     <t>1561: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (#52-6 &gt; 50-22)</t>
   </si>
   <si>
-    <t>Dim.LocalDrug.DrugNameWithoutDoseIEN
-Dim.LocalDrug.NationalDrugIEN
-Dim.LocalDrug.NationalDrugIEN</t>
+    <t>Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
     <t>MedicationDispense.medication[x]:medicationCodeableConcept.coding.display</t>
@@ -915,13 +913,7 @@
     <t>1560: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (#52-6 &gt; 50-.01)</t>
   </si>
   <si>
-    <t>Dim.IVAdditiveIngredient.LocalDrugNameWithDose
-Dim.IVSolutionIngredient.LocalDrugNameWithDose
-Dim.LocalDrug.CorrespondingInpatientLocalDrugNameWithDose
-Dim.LocalDrug.CorrespondingOutpatientLocalDrugNameWithDose
-Dim.LocalDrug.LocalDrugNameWithDose
-Dim.LocalDrug.LocalDrugNameWithDose
-RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
+    <t>Dim.IVAdditiveIngredient.LocalDrugNameWithDose,Dim.IVSolutionIngredient.LocalDrugNameWithDose,Dim.LocalDrug.CorrespondingInpatientLocalDrugNameWithDose,Dim.LocalDrug.CorrespondingOutpatientLocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
   </si>
   <si>
     <t>MedicationDispense.subject</t>
@@ -2633,7 +2625,7 @@
     <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="149.8671875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="61.98046875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="255.0" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="40.984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,15 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
+    <t>Mapping: Virtual Patient Record (VPR)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -250,15 +259,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t/>
@@ -545,6 +545,9 @@
     <t>http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1</t>
   </si>
   <si>
+    <t>1555: fixed value = #in-progress when PRESCRIPTION - RELEASED DATE/TIME (#52-31) case null</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -555,9 +558,6 @@
   </si>
   <si>
     <t>CombinedMedicationDispense.SupplyEvent.statusCode</t>
-  </si>
-  <si>
-    <t>1555: fixed value = #in-progress when PRESCRIPTION - RELEASED DATE/TIME (#52-31) case null</t>
   </si>
   <si>
     <t>MedicationDispense.statusReason[x]</t>
@@ -816,16 +816,16 @@
     <t>Coding.code</t>
   </si>
   <si>
+    <t>1561: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (#52-6 &gt; 50-22)</t>
+  </si>
+  <si>
+    <t>Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
     <t>C*E.1</t>
-  </si>
-  <si>
-    <t>1561: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (#52-6 &gt; 50-22)</t>
-  </si>
-  <si>
-    <t>Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
     <t>MedicationDispense.medication[x]:medicationCodeableConcept.coding.display</t>
@@ -904,16 +904,16 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>1560: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (#52-6 &gt; 50-.01)</t>
+  </si>
+  <si>
+    <t>Dim.IVAdditiveIngredient.LocalDrugNameWithDose,Dim.IVSolutionIngredient.LocalDrugNameWithDose,Dim.LocalDrug.CorrespondingInpatientLocalDrugNameWithDose,Dim.LocalDrug.CorrespondingOutpatientLocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
+  </si>
+  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>1560: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (#52-6 &gt; 50-.01)</t>
-  </si>
-  <si>
-    <t>Dim.IVAdditiveIngredient.LocalDrugNameWithDose,Dim.IVSolutionIngredient.LocalDrugNameWithDose,Dim.LocalDrug.CorrespondingInpatientLocalDrugNameWithDose,Dim.LocalDrug.CorrespondingOutpatientLocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
   </si>
   <si>
     <t>MedicationDispense.subject</t>
@@ -932,6 +932,9 @@
     <t>SubstanceAdministration-&gt;subject-&gt;Patient.</t>
   </si>
   <si>
+    <t>1551: reference from PRESCRIPTION - PATIENT (#52-2)</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -942,9 +945,6 @@
   </si>
   <si>
     <t>PID-3-Patient ID List</t>
-  </si>
-  <si>
-    <t>1551: reference from PRESCRIPTION - PATIENT (#52-2)</t>
   </si>
   <si>
     <t>MedicationDispense.context</t>
@@ -1061,13 +1061,13 @@
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
+    <t>1715: reference from PRESCRIPTION - REFILL &gt; REFILL - DIVISION (#52-52 &gt; 52.1-8)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
     <t>.role</t>
-  </si>
-  <si>
-    <t>1715: reference from PRESCRIPTION - REFILL &gt; REFILL - DIVISION (#52-52 &gt; 52.1-8)</t>
   </si>
   <si>
     <t>MedicationDispense.location</t>
@@ -1083,16 +1083,16 @@
     <t>The principal physical location where the dispense was performed.</t>
   </si>
   <si>
+    <t>1552: reference from PRESCRIPTION - CLINIC (#52-5)</t>
+  </si>
+  <si>
+    <t>RxOut.RxOutpatFill.PrescribingDivisionIEN</t>
+  </si>
+  <si>
+    <t>Pharmacy: facility</t>
+  </si>
+  <si>
     <t>.participation[typeCode=LOC].role</t>
-  </si>
-  <si>
-    <t>1552: reference from PRESCRIPTION - CLINIC (#52-5)</t>
-  </si>
-  <si>
-    <t>RxOut.RxOutpatFill.PrescribingDivisionIEN</t>
-  </si>
-  <si>
-    <t>Pharmacy: facility</t>
   </si>
   <si>
     <t>MedicationDispense.authorizingPrescription</t>
@@ -1111,6 +1111,12 @@
     <t>Maps to basedOn in Event logical model.</t>
   </si>
   <si>
+    <t>1553: source value from PRESCRIPTION - PLACER ORDER # (#52-39.3)</t>
+  </si>
+  <si>
+    <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
   </si>
   <si>
@@ -1121,12 +1127,6 @@
   </si>
   <si>
     <t>ORC-2 Placer Order Number</t>
-  </si>
-  <si>
-    <t>1553: source value from PRESCRIPTION - PLACER ORDER # (#52-39.3)</t>
-  </si>
-  <si>
-    <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
   </si>
   <si>
     <t>MedicationDispense.type</t>
@@ -1148,6 +1148,9 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType</t>
   </si>
   <si>
+    <t>1709: fixed value = #RF</t>
+  </si>
+  <si>
     <t>.code</t>
   </si>
   <si>
@@ -1155,9 +1158,6 @@
   </si>
   <si>
     <t>RXD-33-Dispense Type</t>
-  </si>
-  <si>
-    <t>1709: fixed value = #RF</t>
   </si>
   <si>
     <t>MedicationDispense.quantity</t>
@@ -1210,16 +1210,16 @@
     <t>Quantity.value</t>
   </si>
   <si>
+    <t>824: source value from PRESCRIPTION - REFILL &gt; REFILL - QTY (#52-52 &gt; 52.1-1)</t>
+  </si>
+  <si>
+    <t>Pharmacy: quantity</t>
+  </si>
+  <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
-  </si>
-  <si>
-    <t>824: source value from PRESCRIPTION - REFILL &gt; REFILL - QTY (#52-52 &gt; 52.1-1)</t>
-  </si>
-  <si>
-    <t>Pharmacy: quantity</t>
   </si>
   <si>
     <t>MedicationDispense.quantity.comparator</t>
@@ -1323,6 +1323,12 @@
   </si>
   <si>
     <t>The amount of medication expressed as a timing amount.</t>
+  </si>
+  <si>
+    <t>827: source value from PRESCRIPTION - REFILL &gt; REFILL - DAYS SUPPLY (#52-52 &gt; 52.1-1.1)</t>
+  </si>
+  <si>
+    <t>Pharmacy: daysSupply</t>
   </si>
   <si>
     <t>effectiveUseTime</t>
@@ -1334,12 +1340,6 @@
 For backwards compatibility, ORC.7 was permitted through v2.6.  Both forms (field and segment) may be present in v2.5, v2.5.1, and v2.6</t>
   </si>
   <si>
-    <t>827: source value from PRESCRIPTION - REFILL &gt; REFILL - DAYS SUPPLY (#52-52 &gt; 52.1-1.1)</t>
-  </si>
-  <si>
-    <t>Pharmacy: daysSupply</t>
-  </si>
-  <si>
     <t>MedicationDispense.whenPrepared</t>
   </si>
   <si>
@@ -1353,6 +1353,9 @@
     <t>The time when the dispensed product was packaged and reviewed.</t>
   </si>
   <si>
+    <t>830: source value from PRESCRIPTION - REFILL &gt; REFILL - REFILL DATE (#52-52 &gt; 52.1-.01)</t>
+  </si>
+  <si>
     <t>.effectiveTime[xmi:type=IVL_TS].low</t>
   </si>
   <si>
@@ -1362,9 +1365,6 @@
     <t>RXD-3-Date/Time Dispensed</t>
   </si>
   <si>
-    <t>830: source value from PRESCRIPTION - REFILL &gt; REFILL - REFILL DATE (#52-52 &gt; 52.1-.01)</t>
-  </si>
-  <si>
     <t>MedicationDispense.whenHandedOver</t>
   </si>
   <si>
@@ -1374,13 +1374,13 @@
     <t>The time the dispensed product was provided to the patient or their representative.</t>
   </si>
   <si>
+    <t>833: source value from PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (#52-52 &gt; 52.1-17)</t>
+  </si>
+  <si>
     <t>Event.occurrence[x]</t>
   </si>
   <si>
     <t>.effectiveTime[xmi:type=IVL_TS].high</t>
-  </si>
-  <si>
-    <t>833: source value from PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (#52-52 &gt; 52.1-17)</t>
   </si>
   <si>
     <t>MedicationDispense.destination</t>
@@ -1593,10 +1593,10 @@
     <t>Annotation.text</t>
   </si>
   <si>
+    <t>1718: source value from PRESCRIPTION - REFILL &gt; REFILL - REMARKS (#52-52 &gt; 52.1-3)</t>
+  </si>
+  <si>
     <t>Act.text</t>
-  </si>
-  <si>
-    <t>1718: source value from PRESCRIPTION - REFILL &gt; REFILL - REMARKS (#52-52 &gt; 52.1-3)</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction</t>
@@ -1668,13 +1668,13 @@
     <t>Dosage.text</t>
   </si>
   <si>
+    <t>1556: source value from PRESCRIPTION - SIG (#52-10)</t>
+  </si>
+  <si>
+    <t>Pharmacy: sig</t>
+  </si>
+  <si>
     <t>RXO-6; RXE-21</t>
-  </si>
-  <si>
-    <t>1556: source value from PRESCRIPTION - SIG (#52-10)</t>
-  </si>
-  <si>
-    <t>Pharmacy: sig</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.additionalInstruction</t>
@@ -2619,14 +2619,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="149.8671875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="149.8671875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="73.296875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2863,19 +2863,19 @@
         <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>81</v>
@@ -3494,16 +3494,16 @@
         <v>81</v>
       </c>
       <c r="AL7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP7" t="s" s="2">
         <v>81</v>
@@ -3620,16 +3620,16 @@
         <v>81</v>
       </c>
       <c r="AL8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO8" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP8" t="s" s="2">
         <v>81</v>
@@ -3746,16 +3746,16 @@
         <v>81</v>
       </c>
       <c r="AL9" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN9" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP9" t="s" s="2">
         <v>81</v>
@@ -3874,16 +3874,16 @@
         <v>81</v>
       </c>
       <c r="AL10" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM10" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN10" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO10" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP10" t="s" s="2">
         <v>81</v>
@@ -3997,25 +3997,25 @@
         <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>81</v>
@@ -4121,19 +4121,19 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>81</v>
@@ -4250,22 +4250,22 @@
         <v>170</v>
       </c>
       <c r="AL13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AP13" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AO13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP13" t="s" s="2">
+      <c r="AQ13" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AQ13" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR13" t="s" s="2">
         <v>81</v>
@@ -4371,19 +4371,19 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>81</v>
@@ -4500,16 +4500,16 @@
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>81</v>
@@ -4621,28 +4621,28 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AQ16" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AR16" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR16" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="17" hidden="true">
@@ -4749,28 +4749,28 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AQ17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AR17" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR17" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -4876,16 +4876,16 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>81</v>
@@ -5002,16 +5002,16 @@
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>81</v>
@@ -5130,25 +5130,25 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR20" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR20" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -5254,16 +5254,16 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>81</v>
@@ -5380,16 +5380,16 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>81</v>
@@ -5508,25 +5508,25 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AM23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR23" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -5634,25 +5634,25 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AM24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR24" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR24" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -5757,10 +5757,10 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>81</v>
+        <v>258</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -5769,16 +5769,16 @@
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>260</v>
+        <v>81</v>
       </c>
       <c r="AQ25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR25" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -5886,25 +5886,25 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AM26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -6014,25 +6014,25 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AM27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR27" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR27" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -6139,10 +6139,10 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>81</v>
+        <v>287</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
@@ -6151,16 +6151,16 @@
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="AQ28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR28" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -6268,25 +6268,25 @@
         <v>296</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AN29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AP29" t="s" s="2">
+      <c r="AQ29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR29" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR29" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -6389,19 +6389,19 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6516,19 +6516,19 @@
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6637,19 +6637,19 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6764,16 +6764,16 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>81</v>
@@ -6890,16 +6890,16 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>81</v>
@@ -7018,16 +7018,16 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>81</v>
@@ -7144,16 +7144,16 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7268,19 +7268,19 @@
         <v>337</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AM37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AO37" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>339</v>
+        <v>81</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -7389,28 +7389,28 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>81</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>81</v>
+        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>345</v>
+        <v>81</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>347</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -7530,13 +7530,13 @@
         <v>356</v>
       </c>
       <c r="AP39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AQ39" t="s" s="2">
+      <c r="AR39" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AR39" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="40" hidden="true">
@@ -7639,28 +7639,28 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>81</v>
+        <v>364</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>364</v>
+        <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AP40" t="s" s="2">
+      <c r="AR40" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="41" hidden="true">
@@ -7766,25 +7766,25 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AM41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AO41" t="s" s="2">
+      <c r="AR41" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="42" hidden="true">
@@ -7890,16 +7890,16 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>81</v>
@@ -8016,16 +8016,16 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>81</v>
@@ -8141,22 +8141,22 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>81</v>
+        <v>384</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>384</v>
+        <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>81</v>
+        <v>385</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
@@ -8272,25 +8272,25 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR45" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR45" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -8398,25 +8398,25 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR46" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR46" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -8524,25 +8524,25 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AM47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR47" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -8652,25 +8652,25 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AM48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR48" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR48" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -8773,22 +8773,22 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>424</v>
+        <v>81</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>81</v>
@@ -8897,28 +8897,28 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>81</v>
+        <v>430</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AO50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AP50" t="s" s="2">
+      <c r="AR50" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -9024,25 +9024,25 @@
         <v>437</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AM51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>431</v>
-      </c>
       <c r="AO51" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AP51" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AR51" t="s" s="2">
-        <v>81</v>
+        <v>433</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -9148,25 +9148,25 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AM52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ52" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AO52" t="s" s="2">
+      <c r="AR52" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR52" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="53" hidden="true">
@@ -9272,16 +9272,16 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>81</v>
@@ -9398,16 +9398,16 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>81</v>
@@ -9524,16 +9524,16 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>81</v>
@@ -9650,16 +9650,16 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>81</v>
@@ -9776,16 +9776,16 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9899,28 +9899,28 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>81</v>
+        <v>473</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AM58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AP58" t="s" s="2">
-        <v>473</v>
+        <v>81</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>474</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" hidden="true">
@@ -10026,22 +10026,22 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AM59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AP59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10147,28 +10147,28 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AM60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO60" t="s" s="2">
+      <c r="AP60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR60" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR60" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="61" hidden="true">
@@ -10274,16 +10274,16 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>81</v>
@@ -10400,16 +10400,16 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>81</v>
@@ -10526,25 +10526,25 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AM63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO63" t="s" s="2">
+      <c r="AP63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR63" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR63" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="64" hidden="true">
@@ -10650,25 +10650,25 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AM64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO64" t="s" s="2">
+      <c r="AP64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR64" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR64" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="65" hidden="true">
@@ -10771,10 +10771,10 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>81</v>
+        <v>507</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>507</v>
+        <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
@@ -10783,16 +10783,16 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR65" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AQ65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR65" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="66" hidden="true">
@@ -10900,16 +10900,16 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO66" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -11024,16 +11024,16 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO67" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>81</v>
@@ -11150,16 +11150,16 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>81</v>
@@ -11278,16 +11278,16 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>81</v>
@@ -11404,25 +11404,25 @@
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="AM70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO70" t="s" s="2">
+      <c r="AP70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR70" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="71" hidden="true">
@@ -11527,22 +11527,22 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>81</v>
+        <v>531</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="AM71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>531</v>
-      </c>
       <c r="AP71" t="s" s="2">
-        <v>532</v>
+        <v>81</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>81</v>
@@ -11658,25 +11658,25 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO72" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="AM72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO72" t="s" s="2">
+      <c r="AP72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR72" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR72" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="73" hidden="true">
@@ -11779,28 +11779,28 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>81</v>
+        <v>547</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO73" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="AM73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO73" t="s" s="2">
+      <c r="AP73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR73" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AQ73" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="AR73" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="74" hidden="true">
@@ -11910,16 +11910,16 @@
         <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO74" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -12036,25 +12036,25 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="AM75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO75" t="s" s="2">
+      <c r="AP75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR75" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="76" hidden="true">
@@ -12164,25 +12164,25 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="AM76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO76" t="s" s="2">
+      <c r="AP76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR76" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR76" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="77" hidden="true">
@@ -12290,25 +12290,25 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO77" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="AM77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO77" t="s" s="2">
+      <c r="AP77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR77" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR77" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="78" hidden="true">
@@ -12418,25 +12418,25 @@
         <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO78" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="AM78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO78" t="s" s="2">
+      <c r="AP78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR78" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR78" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="79" hidden="true">
@@ -12551,16 +12551,16 @@
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR79" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR79" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="80" hidden="true">
@@ -12666,16 +12666,16 @@
         <v>81</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO80" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>81</v>
@@ -12792,16 +12792,16 @@
         <v>81</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>81</v>
@@ -12927,16 +12927,16 @@
         <v>81</v>
       </c>
       <c r="AO82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR82" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR82" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="83" hidden="true">
@@ -13044,25 +13044,25 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO83" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="AM83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO83" t="s" s="2">
+      <c r="AP83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR83" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR83" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="84" hidden="true">
@@ -13174,25 +13174,25 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="AM84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO84" t="s" s="2">
+      <c r="AP84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR84" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR84" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="85" hidden="true">
@@ -13298,16 +13298,16 @@
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO85" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>81</v>
@@ -13424,16 +13424,16 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO86" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>81</v>
@@ -13549,28 +13549,28 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>81</v>
+        <v>635</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>384</v>
+        <v>636</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>81</v>
+        <v>637</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>635</v>
+        <v>81</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>636</v>
+        <v>81</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>637</v>
+        <v>387</v>
       </c>
     </row>
     <row r="88" hidden="true">
@@ -13680,25 +13680,25 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO88" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AM88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO88" t="s" s="2">
+      <c r="AP88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR88" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR88" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="89" hidden="true">
@@ -13803,28 +13803,28 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>81</v>
+        <v>642</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO89" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AM89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO89" t="s" s="2">
+      <c r="AP89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR89" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="AQ89" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AR89" t="s" s="2">
-        <v>644</v>
       </c>
     </row>
     <row r="90" hidden="true">
@@ -13932,25 +13932,25 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AM90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO90" t="s" s="2">
+      <c r="AP90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR90" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR90" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="91" hidden="true">
@@ -14055,28 +14055,28 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>81</v>
+        <v>650</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AM91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO91" t="s" s="2">
+      <c r="AP91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR91" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AQ91" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AR91" t="s" s="2">
-        <v>644</v>
       </c>
     </row>
     <row r="92" hidden="true">
@@ -14186,25 +14186,25 @@
         <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="AM92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO92" t="s" s="2">
+      <c r="AP92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR92" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR92" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="93" hidden="true">
@@ -14314,25 +14314,25 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="AM93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO93" t="s" s="2">
+      <c r="AP93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR93" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR93" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="94" hidden="true">
@@ -14442,16 +14442,16 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO94" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14568,16 +14568,16 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO95" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14692,22 +14692,22 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO96" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="AM96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AP96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ96" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ96" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14816,16 +14816,16 @@
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO97" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>81</v>
@@ -14942,16 +14942,16 @@
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO98" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>81</v>
@@ -15070,16 +15070,16 @@
         <v>81</v>
       </c>
       <c r="AL99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>81</v>
@@ -15194,16 +15194,16 @@
         <v>81</v>
       </c>
       <c r="AL100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO100" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15318,25 +15318,25 @@
         <v>81</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>364</v>
+        <v>81</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="AO101" t="s" s="2">
+      <c r="AR101" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR101" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="102" hidden="true">
@@ -15442,22 +15442,22 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO102" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="AM102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN102" t="s" s="2">
+      <c r="AP102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15566,22 +15566,22 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO103" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="AM103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN103" t="s" s="2">
+      <c r="AP103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ103" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15692,16 +15692,16 @@
         <v>81</v>
       </c>
       <c r="AL104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO104" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15818,16 +15818,16 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO105" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION (#52) to MedicationDispense</t>
+    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION (52) to MedicationDispense</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -545,7 +545,7 @@
     <t>http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1</t>
   </si>
   <si>
-    <t>1555: fixed value = #in-progress when PRESCRIPTION - RELEASED DATE/TIME (#52-31) case null</t>
+    <t>1555: fixed value = #in-progress when PRESCRIPTION - RELEASED DATE/TIME (52-31) case null</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -816,7 +816,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1561: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (#52-6 &gt; 50-22)</t>
+    <t>1561: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (52-6 &gt; 50-22)</t>
   </si>
   <si>
     <t>Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
@@ -904,7 +904,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1560: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (#52-6 &gt; 50-.01)</t>
+    <t>1560: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (52-6 &gt; 50-.01)</t>
   </si>
   <si>
     <t>Dim.IVAdditiveIngredient.LocalDrugNameWithDose,Dim.IVSolutionIngredient.LocalDrugNameWithDose,Dim.LocalDrug.CorrespondingInpatientLocalDrugNameWithDose,Dim.LocalDrug.CorrespondingOutpatientLocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
@@ -932,7 +932,7 @@
     <t>SubstanceAdministration-&gt;subject-&gt;Patient.</t>
   </si>
   <si>
-    <t>1551: reference from PRESCRIPTION - PATIENT (#52-2)</t>
+    <t>1551: reference from PRESCRIPTION - PATIENT (52-2)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1061,7 +1061,7 @@
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
-    <t>1715: reference from PRESCRIPTION - REFILL &gt; REFILL - DIVISION (#52-52 &gt; 52.1-8)</t>
+    <t>1715: reference from PRESCRIPTION - REFILL &gt; REFILL - DIVISION (52-52 &gt; 52.1-8)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1083,7 +1083,7 @@
     <t>The principal physical location where the dispense was performed.</t>
   </si>
   <si>
-    <t>1552: reference from PRESCRIPTION - CLINIC (#52-5)</t>
+    <t>1552: reference from PRESCRIPTION - CLINIC (52-5)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatFill.PrescribingDivisionIEN</t>
@@ -1111,7 +1111,7 @@
     <t>Maps to basedOn in Event logical model.</t>
   </si>
   <si>
-    <t>1553: source value from PRESCRIPTION - PLACER ORDER # (#52-39.3)</t>
+    <t>1553: source value from PRESCRIPTION - PLACER ORDER # (52-39.3)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
@@ -1210,7 +1210,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>824: source value from PRESCRIPTION - REFILL &gt; REFILL - QTY (#52-52 &gt; 52.1-1)</t>
+    <t>824: source value from PRESCRIPTION - REFILL &gt; REFILL - QTY (52-52 &gt; 52.1-1)</t>
   </si>
   <si>
     <t>Pharmacy: quantity</t>
@@ -1325,7 +1325,7 @@
     <t>The amount of medication expressed as a timing amount.</t>
   </si>
   <si>
-    <t>827: source value from PRESCRIPTION - REFILL &gt; REFILL - DAYS SUPPLY (#52-52 &gt; 52.1-1.1)</t>
+    <t>827: source value from PRESCRIPTION - REFILL &gt; REFILL - DAYS SUPPLY (52-52 &gt; 52.1-1.1)</t>
   </si>
   <si>
     <t>Pharmacy: daysSupply</t>
@@ -1353,7 +1353,7 @@
     <t>The time when the dispensed product was packaged and reviewed.</t>
   </si>
   <si>
-    <t>830: source value from PRESCRIPTION - REFILL &gt; REFILL - REFILL DATE (#52-52 &gt; 52.1-.01)</t>
+    <t>830: source value from PRESCRIPTION - REFILL &gt; REFILL - REFILL DATE (52-52 &gt; 52.1-.01)</t>
   </si>
   <si>
     <t>.effectiveTime[xmi:type=IVL_TS].low</t>
@@ -1374,7 +1374,7 @@
     <t>The time the dispensed product was provided to the patient or their representative.</t>
   </si>
   <si>
-    <t>833: source value from PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (#52-52 &gt; 52.1-17)</t>
+    <t>833: source value from PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (52-52 &gt; 52.1-17)</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -1487,7 +1487,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>836: source value from PRESCRIPTION - REFILL &gt; REFILL - MAIL/WINDOW (#52-52 &gt; 52.1-2)</t>
+    <t>836: source value from PRESCRIPTION - REFILL &gt; REFILL - MAIL/WINDOW (52-52 &gt; 52.1-2)</t>
   </si>
   <si>
     <t>Pharmacy: routing</t>
@@ -1593,7 +1593,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>1718: source value from PRESCRIPTION - REFILL &gt; REFILL - REMARKS (#52-52 &gt; 52.1-3)</t>
+    <t>1718: source value from PRESCRIPTION - REFILL &gt; REFILL - REMARKS (52-52 &gt; 52.1-3)</t>
   </si>
   <si>
     <t>Act.text</t>
@@ -1668,7 +1668,7 @@
     <t>Dosage.text</t>
   </si>
   <si>
-    <t>1556: source value from PRESCRIPTION - SIG (#52-10)</t>
+    <t>1556: source value from PRESCRIPTION - SIG (52-10)</t>
   </si>
   <si>
     <t>Pharmacy: sig</t>
@@ -1716,7 +1716,7 @@
     <t>Dosage.patientInstruction</t>
   </si>
   <si>
-    <t>1557: source value from PRESCRIPTION - PATIENT INSTRUCTIONS (#52-114)</t>
+    <t>1557: source value from PRESCRIPTION - PATIENT INSTRUCTIONS (52-114)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatSig.PatientInstructions</t>
@@ -1986,7 +1986,7 @@
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].value</t>
   </si>
   <si>
-    <t>1558: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (#52-113 &gt; 52.0113-.01) case number</t>
+    <t>1558: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (52-113 &gt; 52.0113-.01) case number</t>
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
@@ -2007,7 +2007,7 @@
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].unit</t>
   </si>
   <si>
-    <t>1559: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (#52-113 &gt; 52.0113-2)</t>
+    <t>1559: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (52-113 &gt; 52.0113-2)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.Unit</t>
@@ -2031,7 +2031,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFDoseUnits</t>
   </si>
   <si>
-    <t>1579: terminologyMaps using VF_DoseUnits on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (#52-113 &gt; 52.0113-2)</t>
+    <t>1579: terminologyMaps using VF_DoseUnits on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (52-113 &gt; 52.0113-2)</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.rate[x]</t>
@@ -2619,7 +2619,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="149.8671875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="148.33203125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1487,7 +1487,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>836: source value from PRESCRIPTION - REFILL &gt; REFILL - MAIL/WINDOW (52-52 &gt; 52.1-2)</t>
+    <t>836: source value from PRESCRIPTION - REFILL &gt; REFILL - MAIL/WINDOW/PARK (52-52 &gt; 52.1-2)</t>
   </si>
   <si>
     <t>Pharmacy: routing</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="723">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -819,7 +819,8 @@
     <t>1561: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (52-6 &gt; 50-22)</t>
   </si>
   <si>
-    <t>Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
+    <t>RxOut.RxOutpat.LocalDrugIEN,RxOut.RxOutpat.NationalDrugIEN,RxOut.RxOutpatFill.LocalDrugIEN,RxOut.RxOutpatFill.NationalDrugIEN
+Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
     <t>./code</t>
@@ -907,7 +908,8 @@
     <t>1560: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (52-6 &gt; 50-.01)</t>
   </si>
   <si>
-    <t>Dim.IVAdditiveIngredient.LocalDrugNameWithDose,Dim.IVSolutionIngredient.LocalDrugNameWithDose,Dim.LocalDrug.CorrespondingInpatientLocalDrugNameWithDose,Dim.LocalDrug.CorrespondingOutpatientLocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
+    <t>RxOut.RxOutpat.LocalDrugIEN,RxOut.RxOutpat.NationalDrugIEN,RxOut.RxOutpatFill.LocalDrugIEN,RxOut.RxOutpatFill.NationalDrugIEN
+Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -935,6 +937,9 @@
     <t>1551: reference from PRESCRIPTION - PATIENT (52-2)</t>
   </si>
   <si>
+    <t>RxOut.ActivityLog.PatientIEN,RxOut.ActivityLogOtherComments.PatientIEN,RxOut.RxOutpat.PatientIEN,RxOut.RxOutpatExt.PatientIEN,RxOut.RxOutpatExt.PatientSID,RxOut.RxOutpatFill.PatientIEN,RxOut.RxOutpatMedInstructions.PatientIEN,RxOut.RxOutpatSig.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1061,9 +1066,6 @@
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
-    <t>1715: reference from PRESCRIPTION - REFILL &gt; REFILL - DIVISION (52-52 &gt; 52.1-8)</t>
-  </si>
-  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1083,13 +1085,7 @@
     <t>The principal physical location where the dispense was performed.</t>
   </si>
   <si>
-    <t>1552: reference from PRESCRIPTION - CLINIC (52-5)</t>
-  </si>
-  <si>
-    <t>RxOut.RxOutpatFill.PrescribingDivisionIEN</t>
-  </si>
-  <si>
-    <t>Pharmacy: facility</t>
+    <t>1715: reference from PRESCRIPTION - REFILL &gt; REFILL - DIVISION (52-52 &gt; 52.1-8)</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role</t>
@@ -1353,7 +1349,7 @@
     <t>The time when the dispensed product was packaged and reviewed.</t>
   </si>
   <si>
-    <t>830: source value from PRESCRIPTION - REFILL &gt; REFILL - REFILL DATE (52-52 &gt; 52.1-.01)</t>
+    <t>833: source value from PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (52-52 &gt; 52.1-17)</t>
   </si>
   <si>
     <t>.effectiveTime[xmi:type=IVL_TS].low</t>
@@ -1372,9 +1368,6 @@
   </si>
   <si>
     <t>The time the dispensed product was provided to the patient or their representative.</t>
-  </si>
-  <si>
-    <t>833: source value from PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (52-52 &gt; 52.1-17)</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -2620,7 +2613,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="148.33203125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
@@ -6268,33 +6261,33 @@
         <v>296</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>81</v>
+        <v>297</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6317,13 +6310,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6374,7 +6367,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6398,10 +6391,10 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6415,10 +6408,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6441,13 +6434,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6498,7 +6491,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6525,10 +6518,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6539,10 +6532,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6565,13 +6558,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6622,7 +6615,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6646,10 +6639,10 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6663,10 +6656,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6787,10 +6780,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6913,14 +6906,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6942,10 +6935,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -7000,7 +6993,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7041,10 +7034,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7070,14 +7063,14 @@
         <v>185</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7105,10 +7098,10 @@
         <v>179</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7126,7 +7119,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7153,7 +7146,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7167,10 +7160,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7184,7 +7177,7 @@
         <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>81</v>
@@ -7193,13 +7186,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7250,7 +7243,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7265,7 +7258,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>337</v>
+        <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -7392,16 +7385,16 @@
         <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7415,10 +7408,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7441,16 +7434,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7500,7 +7493,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7515,36 +7508,36 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AR39" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AR39" t="s" s="2">
-        <v>358</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7570,10 +7563,10 @@
         <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7585,7 +7578,7 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>81</v>
@@ -7603,11 +7596,11 @@
         <v>179</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>363</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
       </c>
@@ -7624,7 +7617,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7639,36 +7632,36 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AP40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AR40" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>367</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7691,13 +7684,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7748,7 +7741,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7775,24 +7768,24 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AP41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AR41" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>374</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7913,10 +7906,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8039,10 +8032,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8065,19 +8058,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8126,7 +8119,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8141,36 +8134,36 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AL44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR44" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR44" t="s" s="2">
-        <v>387</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8196,20 +8189,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8233,28 +8226,28 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8281,7 +8274,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8290,15 +8283,15 @@
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8324,14 +8317,14 @@
         <v>210</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8380,7 +8373,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8407,7 +8400,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8416,15 +8409,15 @@
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8450,14 +8443,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8506,7 +8499,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8515,7 +8508,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8533,7 +8526,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8542,15 +8535,15 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8576,16 +8569,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8634,7 +8627,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8661,7 +8654,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8670,15 +8663,15 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8701,13 +8694,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8758,7 +8751,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8773,36 +8766,36 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>425</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8825,13 +8818,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8882,7 +8875,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8897,36 +8890,36 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO50" t="s" s="2">
+      <c r="AR50" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>433</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8940,7 +8933,7 @@
         <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>81</v>
@@ -8949,13 +8942,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9006,7 +8999,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9021,7 +9014,7 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>81</v>
@@ -9030,27 +9023,27 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9076,10 +9069,10 @@
         <v>341</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9130,7 +9123,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9157,24 +9150,24 @@
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9295,10 +9288,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9421,10 +9414,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9450,13 +9443,13 @@
         <v>210</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9506,7 +9499,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9515,7 +9508,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9547,10 +9540,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9576,13 +9569,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9608,31 +9601,31 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9673,10 +9666,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9702,13 +9695,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9758,7 +9751,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9785,7 +9778,7 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9799,10 +9792,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9828,13 +9821,13 @@
         <v>210</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9884,7 +9877,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9899,13 +9892,13 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9925,10 +9918,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9951,13 +9944,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10008,7 +10001,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10035,13 +10028,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10049,10 +10042,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10075,13 +10068,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10132,7 +10125,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10156,10 +10149,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10168,15 +10161,15 @@
         <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10297,10 +10290,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10423,10 +10416,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10449,16 +10442,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10508,7 +10501,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10535,7 +10528,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10549,10 +10542,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10575,13 +10568,13 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10632,7 +10625,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10659,7 +10652,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10673,10 +10666,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10699,13 +10692,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10756,7 +10749,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10771,7 +10764,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10783,7 +10776,7 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10797,10 +10790,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10823,16 +10816,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10882,7 +10875,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10909,7 +10902,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10923,10 +10916,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11047,10 +11040,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11173,14 +11166,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11202,10 +11195,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11260,7 +11253,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11301,10 +11294,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11327,17 +11320,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11386,7 +11379,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11413,7 +11406,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11422,15 +11415,15 @@
         <v>81</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11456,14 +11449,14 @@
         <v>210</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11512,7 +11505,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11527,19 +11520,19 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>81</v>
@@ -11548,15 +11541,15 @@
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11582,16 +11575,16 @@
         <v>185</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="O72" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11619,10 +11612,10 @@
         <v>179</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11640,7 +11633,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11667,7 +11660,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11676,15 +11669,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11710,10 +11703,10 @@
         <v>210</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11764,7 +11757,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11779,10 +11772,10 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11791,7 +11784,7 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11800,15 +11793,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11831,19 +11824,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11892,7 +11885,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11919,7 +11912,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11933,10 +11926,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11959,16 +11952,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11997,10 +11990,10 @@
         <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12018,7 +12011,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12045,7 +12038,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12054,15 +12047,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12088,16 +12081,16 @@
         <v>185</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O76" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12125,10 +12118,10 @@
         <v>179</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12146,7 +12139,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12173,7 +12166,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12182,15 +12175,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12216,14 +12209,14 @@
         <v>185</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12251,10 +12244,10 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12272,7 +12265,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12299,7 +12292,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12308,15 +12301,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12342,16 +12335,16 @@
         <v>185</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="O78" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12379,10 +12372,10 @@
         <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12400,7 +12393,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12427,7 +12420,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12436,15 +12429,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12467,13 +12460,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12524,7 +12517,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12560,15 +12553,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12689,10 +12682,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12815,10 +12808,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12844,14 +12837,14 @@
         <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12879,10 +12872,10 @@
         <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12900,7 +12893,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12936,15 +12929,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12967,19 +12960,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13026,7 +13019,7 @@
         <v>200</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13053,7 +13046,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13062,18 +13055,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13095,19 +13088,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13156,7 +13149,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13165,42 +13158,42 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR84" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR84" t="s" s="2">
-        <v>628</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13321,10 +13314,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13447,10 +13440,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13473,19 +13466,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13534,7 +13527,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13549,19 +13542,19 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>81</v>
@@ -13570,15 +13563,15 @@
         <v>81</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13604,20 +13597,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13641,28 +13634,28 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13689,7 +13682,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13698,15 +13691,15 @@
         <v>81</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13732,14 +13725,14 @@
         <v>210</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13788,7 +13781,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13803,19 +13796,19 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>81</v>
@@ -13824,15 +13817,15 @@
         <v>81</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13858,14 +13851,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13914,7 +13907,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13923,7 +13916,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13941,7 +13934,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13950,15 +13943,15 @@
         <v>81</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13984,16 +13977,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14022,7 +14015,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14040,7 +14033,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14055,19 +14048,19 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>81</v>
@@ -14076,15 +14069,15 @@
         <v>81</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14107,19 +14100,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14168,7 +14161,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14195,7 +14188,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14204,15 +14197,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14235,19 +14228,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14296,7 +14289,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14323,7 +14316,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14332,15 +14325,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14363,19 +14356,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="O94" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>673</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14424,7 +14417,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14451,7 +14444,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14465,10 +14458,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14491,17 +14484,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14550,7 +14543,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14577,7 +14570,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14591,10 +14584,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14617,13 +14610,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14674,7 +14667,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14701,13 +14694,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14715,10 +14708,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14839,10 +14832,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14965,14 +14958,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14994,10 +14987,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15052,7 +15045,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15093,10 +15086,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15122,10 +15115,10 @@
         <v>272</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15176,7 +15169,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15203,7 +15196,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15217,10 +15210,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15246,10 +15239,10 @@
         <v>185</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15279,10 +15272,10 @@
         <v>179</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15300,7 +15293,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15327,24 +15320,24 @@
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15370,10 +15363,10 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15403,10 +15396,10 @@
         <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15424,7 +15417,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15451,13 +15444,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15465,10 +15458,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15491,13 +15484,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15548,7 +15541,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15575,13 +15568,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15589,14 +15582,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15615,16 +15608,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15674,7 +15667,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15701,7 +15694,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15715,10 +15708,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15741,16 +15734,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>724</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15800,7 +15793,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15827,7 +15820,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="725">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -765,7 +765,13 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>urn:oid:2.16.840.1.113883.6.233</t>
+  </si>
+  <si>
     <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1561-1: fixed value = urn:oid:2.16.840.1.113883.6.233</t>
   </si>
   <si>
     <t>./codeSystem</t>
@@ -5413,7 +5419,7 @@
         <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>81</v>
@@ -5444,7 +5450,7 @@
         <v>81</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>81</v>
+        <v>241</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>81</v>
@@ -5483,7 +5489,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5498,7 +5504,7 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
@@ -5510,7 +5516,7 @@
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>81</v>
@@ -5519,15 +5525,15 @@
         <v>81</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5553,13 +5559,13 @@
         <v>210</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5609,7 +5615,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5636,7 +5642,7 @@
         <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>81</v>
@@ -5645,15 +5651,15 @@
         <v>81</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5679,14 +5685,14 @@
         <v>111</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5735,7 +5741,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5750,10 +5756,10 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -5762,7 +5768,7 @@
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -5771,15 +5777,15 @@
         <v>81</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5805,14 +5811,14 @@
         <v>210</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5861,7 +5867,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5888,7 +5894,7 @@
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>81</v>
@@ -5897,15 +5903,15 @@
         <v>81</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5928,19 +5934,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5989,7 +5995,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6016,7 +6022,7 @@
         <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>81</v>
@@ -6025,15 +6031,15 @@
         <v>81</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6059,16 +6065,16 @@
         <v>210</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -6117,7 +6123,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6132,10 +6138,10 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
@@ -6144,7 +6150,7 @@
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>81</v>
@@ -6153,15 +6159,15 @@
         <v>81</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6184,16 +6190,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6243,7 +6249,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6258,36 +6264,36 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6310,13 +6316,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6367,7 +6373,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6391,10 +6397,10 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6408,10 +6414,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6434,13 +6440,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6491,7 +6497,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6518,10 +6524,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6532,10 +6538,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6558,13 +6564,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6615,7 +6621,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6639,10 +6645,10 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6656,10 +6662,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6780,10 +6786,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6906,14 +6912,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6935,10 +6941,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -6993,7 +6999,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7034,10 +7040,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7063,14 +7069,14 @@
         <v>185</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7098,10 +7104,10 @@
         <v>179</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7119,7 +7125,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7146,7 +7152,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7160,10 +7166,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7186,13 +7192,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7243,7 +7249,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7267,10 +7273,10 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>81</v>
@@ -7284,10 +7290,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7310,13 +7316,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7367,7 +7373,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7382,7 +7388,7 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -7394,7 +7400,7 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7408,10 +7414,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7434,16 +7440,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7493,7 +7499,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7508,36 +7514,36 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7563,10 +7569,10 @@
         <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7578,7 +7584,7 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>81</v>
@@ -7596,28 +7602,28 @@
         <v>179</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7632,7 +7638,7 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -7644,24 +7650,24 @@
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7684,13 +7690,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7741,7 +7747,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7768,24 +7774,24 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7906,10 +7912,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8032,10 +8038,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8058,19 +8064,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8119,7 +8125,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8134,19 +8140,19 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -8155,15 +8161,15 @@
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8189,20 +8195,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8226,10 +8232,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8247,7 +8253,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8274,7 +8280,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8283,15 +8289,15 @@
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8317,14 +8323,14 @@
         <v>210</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8373,7 +8379,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8400,7 +8406,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8409,15 +8415,15 @@
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8443,14 +8449,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8499,7 +8505,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8508,7 +8514,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8526,7 +8532,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8535,15 +8541,15 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8569,16 +8575,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8627,7 +8633,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8654,7 +8660,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8663,15 +8669,15 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8694,13 +8700,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8751,7 +8757,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8766,19 +8772,19 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>81</v>
@@ -8787,15 +8793,15 @@
         <v>81</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8818,13 +8824,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8875,7 +8881,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8890,7 +8896,7 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
@@ -8902,24 +8908,24 @@
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8942,13 +8948,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8999,7 +9005,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9023,27 +9029,27 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9066,13 +9072,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9123,7 +9129,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9150,24 +9156,24 @@
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9288,10 +9294,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9414,10 +9420,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9443,13 +9449,13 @@
         <v>210</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9499,7 +9505,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9508,7 +9514,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9540,10 +9546,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9569,13 +9575,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9601,13 +9607,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9625,7 +9631,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9666,10 +9672,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9695,13 +9701,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9751,7 +9757,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9778,7 +9784,7 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9792,10 +9798,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9821,13 +9827,13 @@
         <v>210</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9877,7 +9883,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9892,13 +9898,13 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9918,10 +9924,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9944,13 +9950,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10001,7 +10007,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10028,13 +10034,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10042,10 +10048,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10068,13 +10074,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10125,7 +10131,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10149,10 +10155,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10161,15 +10167,15 @@
         <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10290,10 +10296,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10416,10 +10422,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10442,16 +10448,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10501,7 +10507,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10528,7 +10534,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10542,10 +10548,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10568,13 +10574,13 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10625,7 +10631,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10652,7 +10658,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10666,10 +10672,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10692,13 +10698,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10749,7 +10755,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10764,7 +10770,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10776,7 +10782,7 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10790,10 +10796,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10816,16 +10822,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10875,7 +10881,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10902,7 +10908,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10916,10 +10922,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11040,10 +11046,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11166,14 +11172,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11195,10 +11201,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11253,7 +11259,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11294,10 +11300,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11320,17 +11326,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11379,7 +11385,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11406,7 +11412,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11415,15 +11421,15 @@
         <v>81</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11449,14 +11455,14 @@
         <v>210</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11505,7 +11511,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11520,19 +11526,19 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>81</v>
@@ -11541,15 +11547,15 @@
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11575,16 +11581,16 @@
         <v>185</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11612,10 +11618,10 @@
         <v>179</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11633,7 +11639,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11660,7 +11666,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11669,15 +11675,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11703,10 +11709,10 @@
         <v>210</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11757,7 +11763,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11772,10 +11778,10 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11784,7 +11790,7 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11793,15 +11799,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11824,19 +11830,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11885,7 +11891,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11912,7 +11918,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11926,10 +11932,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11952,16 +11958,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11990,10 +11996,10 @@
         <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12011,7 +12017,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12038,7 +12044,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12047,15 +12053,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12081,16 +12087,16 @@
         <v>185</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12118,10 +12124,10 @@
         <v>179</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12139,7 +12145,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12166,7 +12172,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12175,15 +12181,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12209,14 +12215,14 @@
         <v>185</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12244,10 +12250,10 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12265,7 +12271,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12292,7 +12298,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12301,15 +12307,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12335,16 +12341,16 @@
         <v>185</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12372,10 +12378,10 @@
         <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12393,7 +12399,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12420,7 +12426,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12429,15 +12435,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12460,13 +12466,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12517,7 +12523,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12553,15 +12559,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12682,10 +12688,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12808,10 +12814,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12837,14 +12843,14 @@
         <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12872,10 +12878,10 @@
         <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12893,7 +12899,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12929,15 +12935,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12960,19 +12966,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13019,7 +13025,7 @@
         <v>200</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13046,7 +13052,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13055,18 +13061,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13088,19 +13094,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13149,7 +13155,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13158,10 +13164,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -13176,7 +13182,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13185,15 +13191,15 @@
         <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13314,10 +13320,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13440,10 +13446,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13466,19 +13472,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13527,7 +13533,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13542,19 +13548,19 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>81</v>
@@ -13563,15 +13569,15 @@
         <v>81</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13597,20 +13603,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13634,10 +13640,10 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13655,7 +13661,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13682,7 +13688,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13691,15 +13697,15 @@
         <v>81</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13725,14 +13731,14 @@
         <v>210</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13781,7 +13787,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13796,19 +13802,19 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>81</v>
@@ -13817,15 +13823,15 @@
         <v>81</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13851,14 +13857,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13907,7 +13913,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13916,7 +13922,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13934,7 +13940,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13943,15 +13949,15 @@
         <v>81</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13977,16 +13983,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14015,7 +14021,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14033,7 +14039,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14048,19 +14054,19 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>81</v>
@@ -14069,15 +14075,15 @@
         <v>81</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14100,19 +14106,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14161,7 +14167,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14188,7 +14194,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14197,15 +14203,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14228,19 +14234,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14289,7 +14295,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14316,7 +14322,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14325,15 +14331,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14356,19 +14362,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14417,7 +14423,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14444,7 +14450,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14458,10 +14464,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14484,17 +14490,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14543,7 +14549,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14570,7 +14576,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14584,10 +14590,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14610,13 +14616,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14667,7 +14673,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14694,13 +14700,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14708,10 +14714,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14832,10 +14838,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14958,14 +14964,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14987,10 +14993,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15045,7 +15051,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15086,10 +15092,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15112,13 +15118,13 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15169,7 +15175,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15196,7 +15202,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15210,10 +15216,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15239,10 +15245,10 @@
         <v>185</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15272,10 +15278,10 @@
         <v>179</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15293,7 +15299,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15320,24 +15326,24 @@
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15363,10 +15369,10 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15396,10 +15402,10 @@
         <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15417,7 +15423,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15444,13 +15450,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15458,10 +15464,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15484,13 +15490,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15541,7 +15547,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15568,13 +15574,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15582,14 +15588,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15608,16 +15614,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15667,7 +15673,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15694,7 +15700,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15708,10 +15714,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15734,16 +15740,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15793,7 +15799,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15820,7 +15826,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1489,7 +1489,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>836: source value from PRESCRIPTION - REFILL &gt; REFILL - MAIL/WINDOW/PARK (52-52 &gt; 52.1-2)</t>
+    <t>1712: source value from PRESCRIPTION - REFILL &gt; REFILL - MAIL/WINDOW/PARK (52-52 &gt; 52.1-2)</t>
   </si>
   <si>
     <t>Pharmacy: routing</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1489,7 +1489,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1712: source value from PRESCRIPTION - REFILL &gt; REFILL - MAIL/WINDOW/PARK (52-52 &gt; 52.1-2)</t>
+    <t>836: source value from PRESCRIPTION - REFILL &gt; REFILL - MAIL/WINDOW/PARK (52-52 &gt; 52.1-2)</t>
   </si>
   <si>
     <t>Pharmacy: routing</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="722">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -829,6 +829,11 @@
 Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
+    <t>Dim.LocalDrug.DrugNameWithoutDoseIEN
+Dim.LocalDrug.NationalDrugIEN
+Dim.LocalDrug.NationalDrugIEN</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
@@ -916,6 +921,11 @@
   <si>
     <t>RxOut.RxOutpat.LocalDrugIEN,RxOut.RxOutpat.NationalDrugIEN,RxOut.RxOutpatFill.LocalDrugIEN,RxOut.RxOutpatFill.NationalDrugIEN
 Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
+  </si>
+  <si>
+    <t>Dim.LocalDrug.LocalDrugNameWithDose
+Dim.LocalDrug.LocalDrugNameWithDose
+RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -1218,9 +1228,6 @@
     <t>824: source value from PRESCRIPTION - REFILL &gt; REFILL - QTY (52-52 &gt; 52.1-1)</t>
   </si>
   <si>
-    <t>Pharmacy: quantity</t>
-  </si>
-  <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
   </si>
   <si>
@@ -1331,9 +1338,6 @@
   </si>
   <si>
     <t>827: source value from PRESCRIPTION - REFILL &gt; REFILL - DAYS SUPPLY (52-52 &gt; 52.1-1.1)</t>
-  </si>
-  <si>
-    <t>Pharmacy: daysSupply</t>
   </si>
   <si>
     <t>effectiveUseTime</t>
@@ -1492,9 +1496,6 @@
     <t>836: source value from PRESCRIPTION - REFILL &gt; REFILL - MAIL/WINDOW/PARK (52-52 &gt; 52.1-2)</t>
   </si>
   <si>
-    <t>Pharmacy: routing</t>
-  </si>
-  <si>
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
@@ -1673,9 +1674,6 @@
     <t>1556: source value from PRESCRIPTION - SIG (52-10)</t>
   </si>
   <si>
-    <t>Pharmacy: sig</t>
-  </si>
-  <si>
     <t>RXO-6; RXE-21</t>
   </si>
   <si>
@@ -1994,9 +1992,6 @@
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
   </si>
   <si>
-    <t>Pharmacy: dose.dose</t>
-  </si>
-  <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.comparator</t>
   </si>
   <si>
@@ -2013,9 +2008,6 @@
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.Unit</t>
-  </si>
-  <si>
-    <t>Pharmacy: dose.units</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.system</t>
@@ -2623,7 +2615,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="148.33203125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="43.37109375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -5765,13 +5757,13 @@
         <v>261</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -5780,15 +5772,15 @@
         <v>81</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5814,14 +5806,14 @@
         <v>210</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5870,7 +5862,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5897,7 +5889,7 @@
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>81</v>
@@ -5906,15 +5898,15 @@
         <v>81</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5937,19 +5929,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5998,7 +5990,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6025,7 +6017,7 @@
         <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>81</v>
@@ -6034,15 +6026,15 @@
         <v>81</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6068,16 +6060,16 @@
         <v>210</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -6126,7 +6118,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6141,19 +6133,19 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>81</v>
+        <v>292</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>81</v>
@@ -6162,15 +6154,15 @@
         <v>81</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6193,16 +6185,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6252,7 +6244,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6267,36 +6259,36 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6319,13 +6311,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6376,7 +6368,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6400,10 +6392,10 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6417,10 +6409,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6443,13 +6435,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6500,7 +6492,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6527,10 +6519,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6541,10 +6533,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6567,13 +6559,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6624,7 +6616,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6639,7 +6631,7 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>81</v>
@@ -6648,10 +6640,10 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6665,10 +6657,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6789,10 +6781,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6915,14 +6907,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6944,10 +6936,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -7002,7 +6994,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7043,10 +7035,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7072,14 +7064,14 @@
         <v>185</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7107,10 +7099,10 @@
         <v>179</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7128,7 +7120,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7155,7 +7147,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7169,10 +7161,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7195,13 +7187,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7252,7 +7244,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7276,10 +7268,10 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>81</v>
@@ -7293,10 +7285,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7319,13 +7311,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7376,7 +7368,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7391,7 +7383,7 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -7403,7 +7395,7 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7417,10 +7409,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7443,16 +7435,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7502,7 +7494,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7517,36 +7509,36 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7572,10 +7564,10 @@
         <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7587,7 +7579,7 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>81</v>
@@ -7605,28 +7597,28 @@
         <v>179</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7641,7 +7633,7 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -7653,24 +7645,24 @@
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7693,13 +7685,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7750,7 +7742,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7777,24 +7769,24 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7915,10 +7907,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8041,10 +8033,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8067,19 +8059,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8128,7 +8120,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8143,19 +8135,19 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -8164,15 +8156,15 @@
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8198,20 +8190,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8235,10 +8227,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8256,7 +8248,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8283,7 +8275,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8292,15 +8284,15 @@
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8326,14 +8318,14 @@
         <v>210</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8382,7 +8374,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8409,7 +8401,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8418,15 +8410,15 @@
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8452,14 +8444,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8508,7 +8500,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8517,7 +8509,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8535,7 +8527,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8544,15 +8536,15 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8578,16 +8570,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8636,7 +8628,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8663,7 +8655,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8672,15 +8664,15 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8703,13 +8695,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8760,7 +8752,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8775,13 +8767,13 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>424</v>
+        <v>81</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -9075,7 +9067,7 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>441</v>
@@ -9907,7 +9899,7 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>474</v>
+        <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9927,10 +9919,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9953,13 +9945,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10010,7 +10002,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10037,13 +10029,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10051,10 +10043,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10077,13 +10069,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10134,7 +10126,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10158,27 +10150,27 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AO60" t="s" s="2">
+      <c r="AP60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR60" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR60" t="s" s="2">
-        <v>487</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10299,10 +10291,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10425,10 +10417,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10451,16 +10443,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10510,7 +10502,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10537,7 +10529,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10551,10 +10543,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10580,10 +10572,10 @@
         <v>428</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10634,7 +10626,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10661,7 +10653,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10675,10 +10667,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10701,13 +10693,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10758,7 +10750,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10773,19 +10765,19 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10799,10 +10791,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10825,16 +10817,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10884,7 +10876,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10911,7 +10903,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10925,10 +10917,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11049,10 +11041,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11175,14 +11167,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11204,10 +11196,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11262,7 +11254,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11303,10 +11295,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11329,17 +11321,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11388,7 +11380,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11415,24 +11407,24 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR70" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>525</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11458,14 +11450,14 @@
         <v>210</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11514,7 +11506,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11529,36 +11521,36 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR71" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR71" t="s" s="2">
-        <v>533</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11584,16 +11576,16 @@
         <v>185</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11621,28 +11613,28 @@
         <v>179</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11669,7 +11661,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11678,15 +11670,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11712,10 +11704,10 @@
         <v>210</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11766,7 +11758,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11781,10 +11773,10 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11793,7 +11785,7 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11802,15 +11794,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11833,19 +11825,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11894,7 +11886,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11921,7 +11913,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11935,10 +11927,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11961,16 +11953,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11999,28 +11991,28 @@
         <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12047,7 +12039,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12056,15 +12048,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12090,16 +12082,16 @@
         <v>185</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12127,28 +12119,28 @@
         <v>179</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12175,7 +12167,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12184,15 +12176,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12218,14 +12210,14 @@
         <v>185</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12253,28 +12245,28 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12301,7 +12293,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12310,15 +12302,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12344,16 +12336,16 @@
         <v>185</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12381,28 +12373,28 @@
         <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12429,7 +12421,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12438,15 +12430,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12469,13 +12461,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12526,7 +12518,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12562,15 +12554,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12691,10 +12683,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12817,10 +12809,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12846,14 +12838,14 @@
         <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12881,28 +12873,28 @@
         <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12938,15 +12930,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12969,19 +12961,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13028,7 +13020,7 @@
         <v>200</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13055,7 +13047,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13064,18 +13056,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13097,19 +13089,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>624</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13158,7 +13150,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13167,42 +13159,42 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="AJ84" t="s" s="2">
+      <c r="AP84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR84" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR84" t="s" s="2">
-        <v>628</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13323,10 +13315,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13449,10 +13441,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13475,19 +13467,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13536,7 +13528,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13551,19 +13543,19 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>81</v>
@@ -13572,15 +13564,15 @@
         <v>81</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13606,20 +13598,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13643,10 +13635,10 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13664,7 +13656,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13691,7 +13683,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13700,15 +13692,15 @@
         <v>81</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13734,14 +13726,14 @@
         <v>210</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13790,7 +13782,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13805,19 +13797,19 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>81</v>
@@ -13826,15 +13818,15 @@
         <v>81</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13860,14 +13852,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13916,7 +13908,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13925,7 +13917,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13943,7 +13935,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13952,15 +13944,15 @@
         <v>81</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13986,16 +13978,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14024,7 +14016,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14042,7 +14034,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14057,19 +14049,19 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>81</v>
@@ -14078,15 +14070,15 @@
         <v>81</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14109,19 +14101,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="O92" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14170,7 +14162,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14197,7 +14189,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14206,15 +14198,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14237,19 +14229,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="O93" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14298,7 +14290,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14325,7 +14317,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14334,15 +14326,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14365,19 +14357,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14426,7 +14418,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14453,7 +14445,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14467,10 +14459,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14493,17 +14485,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14552,7 +14544,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14579,7 +14571,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14593,10 +14585,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14619,13 +14611,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14676,7 +14668,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14703,13 +14695,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14717,10 +14709,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14841,10 +14833,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14967,14 +14959,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14996,10 +14988,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15054,7 +15046,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15095,10 +15087,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15121,13 +15113,13 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15178,7 +15170,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15205,7 +15197,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15219,10 +15211,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15248,10 +15240,10 @@
         <v>185</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15281,10 +15273,10 @@
         <v>179</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15302,7 +15294,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15329,24 +15321,24 @@
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15372,10 +15364,10 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15405,10 +15397,10 @@
         <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15426,7 +15418,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15453,13 +15445,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15467,10 +15459,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15493,13 +15485,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15550,7 +15542,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15577,13 +15569,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15591,14 +15583,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15617,16 +15609,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15676,7 +15668,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15703,7 +15695,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15717,10 +15709,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15743,16 +15735,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15802,7 +15794,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15829,7 +15821,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="726">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -829,11 +829,6 @@
 Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
-    <t>Dim.LocalDrug.DrugNameWithoutDoseIEN
-Dim.LocalDrug.NationalDrugIEN
-Dim.LocalDrug.NationalDrugIEN</t>
-  </si>
-  <si>
     <t>./code</t>
   </si>
   <si>
@@ -923,11 +918,6 @@
 Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
   </si>
   <si>
-    <t>Dim.LocalDrug.LocalDrugNameWithDose
-Dim.LocalDrug.LocalDrugNameWithDose
-RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
-  </si>
-  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
@@ -937,7 +927,7 @@
     <t>MedicationDispense.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1228,6 +1218,9 @@
     <t>824: source value from PRESCRIPTION - REFILL &gt; REFILL - QTY (52-52 &gt; 52.1-1)</t>
   </si>
   <si>
+    <t>Pharmacy: quantity</t>
+  </si>
+  <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
   </si>
   <si>
@@ -1338,6 +1331,9 @@
   </si>
   <si>
     <t>827: source value from PRESCRIPTION - REFILL &gt; REFILL - DAYS SUPPLY (52-52 &gt; 52.1-1.1)</t>
+  </si>
+  <si>
+    <t>Pharmacy: daysSupply</t>
   </si>
   <si>
     <t>effectiveUseTime</t>
@@ -1496,6 +1492,9 @@
     <t>836: source value from PRESCRIPTION - REFILL &gt; REFILL - MAIL/WINDOW/PARK (52-52 &gt; 52.1-2)</t>
   </si>
   <si>
+    <t>Pharmacy: routing</t>
+  </si>
+  <si>
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
@@ -1674,6 +1673,9 @@
     <t>1556: source value from PRESCRIPTION - SIG (52-10)</t>
   </si>
   <si>
+    <t>Pharmacy: sig</t>
+  </si>
+  <si>
     <t>RXO-6; RXE-21</t>
   </si>
   <si>
@@ -1992,6 +1994,9 @@
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
   </si>
   <si>
+    <t>Pharmacy: dose.dose</t>
+  </si>
+  <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.comparator</t>
   </si>
   <si>
@@ -2008,6 +2013,9 @@
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.Unit</t>
+  </si>
+  <si>
+    <t>Pharmacy: dose.units</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.system</t>
@@ -2615,7 +2623,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="148.33203125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="43.37109375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -5757,30 +5765,30 @@
         <v>261</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR25" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>264</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5806,14 +5814,14 @@
         <v>210</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5862,7 +5870,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5889,24 +5897,24 @@
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AP26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>272</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5929,19 +5937,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5990,7 +5998,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6017,24 +6025,24 @@
         <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR27" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR27" t="s" s="2">
-        <v>282</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6060,16 +6068,16 @@
         <v>210</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -6118,7 +6126,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6133,36 +6141,36 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR28" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>294</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6185,16 +6193,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6244,7 +6252,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6259,36 +6267,36 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AM29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AQ29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR29" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR29" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6311,13 +6319,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6368,7 +6376,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6392,10 +6400,10 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6409,10 +6417,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6435,13 +6443,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6492,7 +6500,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6519,10 +6527,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6533,10 +6541,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6559,13 +6567,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6616,7 +6624,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6631,19 +6639,19 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6657,10 +6665,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6781,10 +6789,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6907,14 +6915,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6936,10 +6944,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -6994,7 +7002,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7035,10 +7043,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7064,14 +7072,14 @@
         <v>185</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7099,10 +7107,10 @@
         <v>179</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7120,7 +7128,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7147,7 +7155,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7161,10 +7169,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7187,13 +7195,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7244,7 +7252,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7268,10 +7276,10 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>81</v>
@@ -7285,10 +7293,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7311,13 +7319,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7368,7 +7376,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7383,7 +7391,7 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -7395,7 +7403,7 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7409,10 +7417,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7435,16 +7443,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7494,7 +7502,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7509,36 +7517,36 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AR39" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AR39" t="s" s="2">
-        <v>361</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7564,10 +7572,10 @@
         <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7579,7 +7587,7 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>81</v>
@@ -7597,11 +7605,11 @@
         <v>179</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>366</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
       </c>
@@ -7618,7 +7626,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7633,36 +7641,36 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AP40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AR40" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>370</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7685,13 +7693,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7742,7 +7750,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7769,24 +7777,24 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AP41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AR41" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>377</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7907,10 +7915,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8033,10 +8041,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8059,19 +8067,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8120,7 +8128,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8135,36 +8143,36 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AL44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR44" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR44" t="s" s="2">
-        <v>389</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8190,20 +8198,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q45" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="P45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q45" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8227,28 +8235,28 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="Z45" t="s" s="2">
+      <c r="AA45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8275,24 +8283,24 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR45" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR45" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8318,14 +8326,14 @@
         <v>210</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8374,7 +8382,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8401,24 +8409,24 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AP46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR46" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR46" t="s" s="2">
-        <v>406</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8444,14 +8452,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8500,7 +8508,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8509,7 +8517,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8527,7 +8535,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8536,15 +8544,15 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8570,16 +8578,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8628,7 +8636,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8655,7 +8663,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8664,15 +8672,15 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8695,13 +8703,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8752,7 +8760,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8767,13 +8775,13 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -9067,7 +9075,7 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>441</v>
@@ -9899,7 +9907,7 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>81</v>
+        <v>474</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9919,10 +9927,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9945,13 +9953,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10002,7 +10010,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10029,13 +10037,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10043,10 +10051,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10069,13 +10077,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10126,7 +10134,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10150,10 +10158,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10162,15 +10170,15 @@
         <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10291,10 +10299,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10417,10 +10425,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10443,16 +10451,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10502,7 +10510,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10529,7 +10537,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10543,10 +10551,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10572,10 +10580,10 @@
         <v>428</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10626,7 +10634,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10653,7 +10661,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10667,10 +10675,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10693,13 +10701,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10750,7 +10758,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10765,7 +10773,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10777,7 +10785,7 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10791,10 +10799,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10817,16 +10825,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10876,7 +10884,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10903,7 +10911,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10917,10 +10925,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11041,10 +11049,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11167,14 +11175,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11196,10 +11204,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11254,7 +11262,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11295,10 +11303,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11321,17 +11329,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11380,7 +11388,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11407,7 +11415,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11416,15 +11424,15 @@
         <v>81</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11450,14 +11458,14 @@
         <v>210</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11506,7 +11514,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11521,19 +11529,19 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>81</v>
@@ -11542,15 +11550,15 @@
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11576,16 +11584,16 @@
         <v>185</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11613,10 +11621,10 @@
         <v>179</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11634,7 +11642,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11661,7 +11669,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11670,15 +11678,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11704,10 +11712,10 @@
         <v>210</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11758,7 +11766,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11773,10 +11781,10 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11785,7 +11793,7 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11794,15 +11802,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11825,19 +11833,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11886,7 +11894,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11913,7 +11921,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11927,10 +11935,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11953,16 +11961,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11991,10 +11999,10 @@
         <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12012,7 +12020,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12039,7 +12047,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12048,15 +12056,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12082,16 +12090,16 @@
         <v>185</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12119,10 +12127,10 @@
         <v>179</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12140,7 +12148,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12167,7 +12175,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12176,15 +12184,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12210,14 +12218,14 @@
         <v>185</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12245,10 +12253,10 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12266,7 +12274,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12293,7 +12301,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12302,15 +12310,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12336,16 +12344,16 @@
         <v>185</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12373,10 +12381,10 @@
         <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12394,7 +12402,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12421,7 +12429,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12430,15 +12438,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12461,13 +12469,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12518,7 +12526,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12554,15 +12562,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12683,10 +12691,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12809,10 +12817,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12838,14 +12846,14 @@
         <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12873,10 +12881,10 @@
         <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12894,7 +12902,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12930,15 +12938,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12961,19 +12969,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13020,7 +13028,7 @@
         <v>200</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13047,7 +13055,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13056,18 +13064,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13089,19 +13097,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13150,7 +13158,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13159,10 +13167,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -13177,7 +13185,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13186,15 +13194,15 @@
         <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13315,10 +13323,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13441,10 +13449,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13467,19 +13475,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13528,7 +13536,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13543,36 +13551,36 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR87" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR87" t="s" s="2">
-        <v>389</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13598,20 +13606,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q88" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q88" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13635,28 +13643,28 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Z88" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="Z88" t="s" s="2">
+      <c r="AA88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13683,24 +13691,24 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR88" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR88" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13726,14 +13734,14 @@
         <v>210</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13782,7 +13790,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13797,36 +13805,36 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR89" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR89" t="s" s="2">
-        <v>406</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13852,14 +13860,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13908,7 +13916,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13917,7 +13925,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13935,7 +13943,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13944,15 +13952,15 @@
         <v>81</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13978,16 +13986,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14016,7 +14024,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14034,7 +14042,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14049,19 +14057,19 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>81</v>
@@ -14070,15 +14078,15 @@
         <v>81</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14101,19 +14109,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14162,7 +14170,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14189,7 +14197,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14198,15 +14206,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14229,19 +14237,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14290,7 +14298,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14317,7 +14325,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14326,15 +14334,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14357,19 +14365,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14418,7 +14426,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14445,7 +14453,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14459,10 +14467,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14485,17 +14493,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14544,7 +14552,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14571,7 +14579,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14585,10 +14593,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14611,13 +14619,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14668,7 +14676,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14695,13 +14703,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14709,10 +14717,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14833,10 +14841,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14959,14 +14967,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14988,10 +14996,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15046,7 +15054,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15087,10 +15095,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15113,13 +15121,13 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15170,7 +15178,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15197,7 +15205,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15211,10 +15219,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15240,10 +15248,10 @@
         <v>185</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15273,28 +15281,28 @@
         <v>179</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="Z101" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15321,24 +15329,24 @@
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15364,10 +15372,10 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15397,28 +15405,28 @@
         <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="Z102" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15445,13 +15453,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15459,10 +15467,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15485,13 +15493,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15542,7 +15550,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15569,13 +15577,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15583,14 +15591,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15609,16 +15617,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15668,7 +15676,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15695,7 +15703,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15709,10 +15717,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15735,16 +15743,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15794,7 +15802,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15821,7 +15829,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="727">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1009,9 +1009,6 @@
     <t>Indicates who or what performed the event.</t>
   </si>
   <si>
-    <t>1729: reference from PRESCRIPTION - PARTIAL DATE &gt; PARTIAL DATE - PHARMACIST NAME (52-60 &gt; 52.2-.05)</t>
-  </si>
-  <si>
     <t>Event.performer</t>
   </si>
   <si>
@@ -1065,7 +1062,7 @@
     <t>MedicationDispense.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|Device|RelatedPerson)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>
@@ -1075,6 +1072,9 @@
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
+    <t>1729: reference from PRESCRIPTION - PARTIAL DATE &gt; PARTIAL DATE - PHARMACIST NAME (52-60 &gt; 52.2-.05)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1084,7 +1084,7 @@
     <t>MedicationDispense.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Location)
 </t>
   </si>
   <si>
@@ -1094,7 +1094,7 @@
     <t>The principal physical location where the dispense was performed.</t>
   </si>
   <si>
-    <t>1715: reference from PRESCRIPTION - REFILL &gt; REFILL - DIVISION (52-52 &gt; 52.1-8)</t>
+    <t>1715: reference from PRESCRIPTION - REFILL &gt; REFILL - DIVISION &gt; OUTPATIENT SITE - DEFAULT ERX CLINIC (52-52 &gt; 52.1-8 &gt; 59-10)</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role</t>
@@ -1386,6 +1386,10 @@
   </si>
   <si>
     <t>MedicationDispense.destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Location)
+</t>
   </si>
   <si>
     <t>Where the medication was sent</t>
@@ -2596,7 +2600,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="77.93359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="56.58984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -6558,7 +6562,7 @@
         <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>81</v>
@@ -6639,19 +6643,19 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6665,10 +6669,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6789,10 +6793,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6915,14 +6919,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6944,10 +6948,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -7002,7 +7006,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7043,10 +7047,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7072,14 +7076,14 @@
         <v>185</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7107,11 +7111,11 @@
         <v>179</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
       </c>
@@ -7128,7 +7132,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7155,7 +7159,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7169,10 +7173,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7186,7 +7190,7 @@
         <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>81</v>
@@ -7195,13 +7199,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7252,7 +7256,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7267,7 +7271,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>81</v>
+        <v>340</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -9075,13 +9079,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>344</v>
+        <v>441</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9159,24 +9163,24 @@
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9297,10 +9301,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9423,10 +9427,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9452,13 +9456,13 @@
         <v>210</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9508,7 +9512,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9517,7 +9521,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9549,10 +9553,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9578,13 +9582,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9610,13 +9614,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9634,7 +9638,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9675,10 +9679,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9704,13 +9708,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9760,7 +9764,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9787,7 +9791,7 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9801,10 +9805,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9830,13 +9834,13 @@
         <v>210</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9886,7 +9890,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9901,13 +9905,13 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9927,10 +9931,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9953,13 +9957,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10010,7 +10014,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10037,13 +10041,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10051,10 +10055,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10077,13 +10081,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10134,7 +10138,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10158,10 +10162,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10170,15 +10174,15 @@
         <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10299,10 +10303,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10425,10 +10429,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10451,16 +10455,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10510,7 +10514,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10537,7 +10541,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10551,10 +10555,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10580,10 +10584,10 @@
         <v>428</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10634,7 +10638,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10661,7 +10665,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10675,10 +10679,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10701,13 +10705,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10758,7 +10762,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10773,7 +10777,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10785,7 +10789,7 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10799,10 +10803,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10825,16 +10829,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10884,7 +10888,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10911,7 +10915,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10925,10 +10929,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11049,10 +11053,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11175,14 +11179,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11204,10 +11208,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11262,7 +11266,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11303,10 +11307,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11329,17 +11333,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11388,7 +11392,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11415,7 +11419,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11424,15 +11428,15 @@
         <v>81</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11458,14 +11462,14 @@
         <v>210</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11514,7 +11518,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11529,19 +11533,19 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>81</v>
@@ -11550,15 +11554,15 @@
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11584,16 +11588,16 @@
         <v>185</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11621,10 +11625,10 @@
         <v>179</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11642,7 +11646,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11669,7 +11673,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11678,15 +11682,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11712,10 +11716,10 @@
         <v>210</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11766,7 +11770,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11781,10 +11785,10 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11793,7 +11797,7 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11802,15 +11806,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11833,19 +11837,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11894,7 +11898,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11921,7 +11925,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11935,10 +11939,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11961,16 +11965,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11999,10 +12003,10 @@
         <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12020,7 +12024,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12047,7 +12051,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12056,15 +12060,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12090,16 +12094,16 @@
         <v>185</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12127,10 +12131,10 @@
         <v>179</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12148,7 +12152,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12175,7 +12179,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12184,15 +12188,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12218,14 +12222,14 @@
         <v>185</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12253,10 +12257,10 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12274,7 +12278,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12301,7 +12305,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12310,15 +12314,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12344,16 +12348,16 @@
         <v>185</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12381,10 +12385,10 @@
         <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12402,7 +12406,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12429,7 +12433,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12438,15 +12442,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12469,13 +12473,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12526,7 +12530,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12562,15 +12566,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12691,10 +12695,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12817,10 +12821,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12846,14 +12850,14 @@
         <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12881,10 +12885,10 @@
         <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12902,7 +12906,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12938,15 +12942,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12969,19 +12973,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13028,7 +13032,7 @@
         <v>200</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13055,7 +13059,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13064,18 +13068,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13100,16 +13104,16 @@
         <v>370</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13158,7 +13162,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13167,10 +13171,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -13185,7 +13189,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13194,15 +13198,15 @@
         <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13323,10 +13327,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13449,10 +13453,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13551,13 +13555,13 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -13577,10 +13581,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13705,10 +13709,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13805,13 +13809,13 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -13831,10 +13835,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13957,10 +13961,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14024,7 +14028,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14057,13 +14061,13 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -14083,10 +14087,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14109,19 +14113,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14170,7 +14174,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14197,7 +14201,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14206,15 +14210,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14237,19 +14241,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14298,7 +14302,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14325,7 +14329,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14334,15 +14338,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14368,16 +14372,16 @@
         <v>370</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14426,7 +14430,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14453,7 +14457,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14467,10 +14471,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14496,14 +14500,14 @@
         <v>370</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14552,7 +14556,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14579,7 +14583,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14593,10 +14597,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14622,10 +14626,10 @@
         <v>317</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14676,7 +14680,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14703,13 +14707,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14717,10 +14721,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14841,10 +14845,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14967,14 +14971,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14996,10 +15000,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15054,7 +15058,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15095,10 +15099,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15124,10 +15128,10 @@
         <v>274</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15178,7 +15182,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15205,7 +15209,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15219,10 +15223,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15248,10 +15252,10 @@
         <v>185</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15281,10 +15285,10 @@
         <v>179</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15302,7 +15306,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15335,18 +15339,18 @@
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15372,10 +15376,10 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15405,10 +15409,10 @@
         <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15426,7 +15430,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15453,13 +15457,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15467,10 +15471,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15493,13 +15497,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15550,7 +15554,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15577,13 +15581,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15591,14 +15595,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15617,16 +15621,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15676,7 +15680,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15703,7 +15707,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15717,10 +15721,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15743,16 +15747,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15802,7 +15806,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15829,7 +15833,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1145,6 +1145,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v3-ActCode"/&gt;
     &lt;code value="RF"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1153,7 +1154,7 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType</t>
   </si>
   <si>
-    <t>1709: fixed value = #RF</t>
+    <t>1709: fixed value = http://terminology.hl7.org/CodeSystem/v3-ActCode#RF</t>
   </si>
   <si>
     <t>.code</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -927,7 +927,7 @@
     <t>MedicationDispense.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(Patient|Group)
 </t>
   </si>
   <si>
@@ -1072,7 +1072,7 @@
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
-    <t>1729: reference from PRESCRIPTION - PARTIAL DATE &gt; PARTIAL DATE - PHARMACIST NAME (52-60 &gt; 52.2-.05)</t>
+    <t>1728: reference from PRESCRIPTION - REFILL &gt; REFILL - PHARMACIST NAME (52-52 &gt; 52.1-4)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1103,7 +1103,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/MedicationRequestOutpatient)
 </t>
   </si>
   <si>
@@ -1116,7 +1116,7 @@
     <t>Maps to basedOn in Event logical model.</t>
   </si>
   <si>
-    <t>1553: source value from PRESCRIPTION - PLACER ORDER # (52-39.3)</t>
+    <t>1553: reference from PRESCRIPTION - PLACER ORDER # (52-39.3)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
@@ -2601,7 +2601,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="56.58984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.37890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2035,7 +2035,7 @@
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].code</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFDoseUnits</t>
+    <t>http://va.gov/fhir/ValueSet/DoseUnits</t>
   </si>
   <si>
     <t>1579: terminologyMaps using VF_DoseUnits on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (52-113 &gt; 52.0113-2)</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="728">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -543,6 +543,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+MedicationDispenseRefill-869:if not null then fixed value #completed {null}MedicationDispenseRefill-819:if null then fixed value #in-progress {null}MedicationDispenseRefill-1555:if null then fixed value #in-progress {null}</t>
   </si>
   <si>
     <t>1555: fixed value = #in-progress when PRESCRIPTION - RELEASED DATE/TIME (52-31) case null</t>
@@ -4251,10 +4255,10 @@
         <v>81</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>81</v>
@@ -4263,16 +4267,16 @@
         <v>81</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR13" t="s" s="2">
         <v>81</v>
@@ -4280,10 +4284,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4306,13 +4310,13 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4339,13 +4343,13 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
@@ -4363,7 +4367,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>82</v>
@@ -4387,10 +4391,10 @@
         <v>81</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>81</v>
@@ -4404,10 +4408,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4430,16 +4434,16 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4468,10 +4472,10 @@
         <v>115</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -4489,7 +4493,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -4516,7 +4520,7 @@
         <v>81</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>81</v>
@@ -4530,10 +4534,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4556,16 +4560,16 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4591,29 +4595,29 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>91</v>
@@ -4637,30 +4641,30 @@
         <v>81</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>81</v>
@@ -4682,16 +4686,16 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4717,13 +4721,13 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
@@ -4741,7 +4745,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>91</v>
@@ -4765,27 +4769,27 @@
         <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4808,13 +4812,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4865,7 +4869,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4892,7 +4896,7 @@
         <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>81</v>
@@ -4906,10 +4910,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4938,7 +4942,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>140</v>
@@ -4979,19 +4983,19 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -5018,7 +5022,7 @@
         <v>81</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>81</v>
@@ -5032,10 +5036,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5058,19 +5062,19 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -5119,7 +5123,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -5146,7 +5150,7 @@
         <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>81</v>
@@ -5155,15 +5159,15 @@
         <v>81</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5186,13 +5190,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5243,7 +5247,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5270,7 +5274,7 @@
         <v>81</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>81</v>
@@ -5284,10 +5288,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5316,7 +5320,7 @@
         <v>138</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>140</v>
@@ -5357,19 +5361,19 @@
         <v>81</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -5396,7 +5400,7 @@
         <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>81</v>
@@ -5410,10 +5414,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5439,16 +5443,16 @@
         <v>105</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -5458,7 +5462,7 @@
         <v>81</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>81</v>
@@ -5497,7 +5501,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5512,7 +5516,7 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
@@ -5524,7 +5528,7 @@
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>81</v>
@@ -5533,15 +5537,15 @@
         <v>81</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5564,16 +5568,16 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5623,7 +5627,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5650,7 +5654,7 @@
         <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>81</v>
@@ -5659,15 +5663,15 @@
         <v>81</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5693,14 +5697,14 @@
         <v>111</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5749,7 +5753,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5764,10 +5768,10 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -5776,7 +5780,7 @@
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -5785,15 +5789,15 @@
         <v>81</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5816,17 +5820,17 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5875,7 +5879,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5902,7 +5906,7 @@
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>81</v>
@@ -5911,15 +5915,15 @@
         <v>81</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5942,19 +5946,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -6003,7 +6007,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6030,7 +6034,7 @@
         <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>81</v>
@@ -6039,15 +6043,15 @@
         <v>81</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6070,19 +6074,19 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -6131,7 +6135,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6146,10 +6150,10 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
@@ -6158,7 +6162,7 @@
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>81</v>
@@ -6167,15 +6171,15 @@
         <v>81</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6198,16 +6202,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6257,7 +6261,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6272,36 +6276,36 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6324,13 +6328,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6381,7 +6385,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6405,10 +6409,10 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6422,10 +6426,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6448,13 +6452,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6505,7 +6509,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6532,10 +6536,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6546,10 +6550,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6572,13 +6576,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6629,7 +6633,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6653,10 +6657,10 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6670,10 +6674,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6696,13 +6700,13 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6753,7 +6757,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6780,7 +6784,7 @@
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>81</v>
@@ -6794,10 +6798,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6826,7 +6830,7 @@
         <v>138</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>140</v>
@@ -6879,7 +6883,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6906,7 +6910,7 @@
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>81</v>
@@ -6920,14 +6924,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6949,10 +6953,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -7007,7 +7011,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7048,10 +7052,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7074,17 +7078,17 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7109,13 +7113,13 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7133,7 +7137,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7160,7 +7164,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7174,10 +7178,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7200,13 +7204,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7257,7 +7261,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7272,7 +7276,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -7281,10 +7285,10 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>81</v>
@@ -7298,10 +7302,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7324,13 +7328,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7381,7 +7385,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7396,7 +7400,7 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -7408,7 +7412,7 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7422,10 +7426,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7448,16 +7452,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7507,7 +7511,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7522,36 +7526,36 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7574,13 +7578,13 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7592,28 +7596,28 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y40" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="T40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>362</v>
-      </c>
       <c r="Z40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -7631,7 +7635,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7646,7 +7650,7 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -7658,24 +7662,24 @@
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7698,13 +7702,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7755,7 +7759,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7782,24 +7786,24 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7822,13 +7826,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7879,7 +7883,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7906,7 +7910,7 @@
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>81</v>
@@ -7920,10 +7924,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7952,7 +7956,7 @@
         <v>138</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>140</v>
@@ -7993,19 +7997,19 @@
         <v>81</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8032,7 +8036,7 @@
         <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>81</v>
@@ -8046,10 +8050,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8072,19 +8076,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8133,7 +8137,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8148,19 +8152,19 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -8169,15 +8173,15 @@
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8203,20 +8207,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8240,10 +8244,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8261,7 +8265,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8288,7 +8292,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8297,15 +8301,15 @@
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8328,17 +8332,17 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8387,7 +8391,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8414,7 +8418,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8423,15 +8427,15 @@
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8457,14 +8461,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8513,7 +8517,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8522,7 +8526,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8540,7 +8544,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8549,15 +8553,15 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8583,16 +8587,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8641,7 +8645,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8668,7 +8672,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8677,15 +8681,15 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8708,13 +8712,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8765,7 +8769,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8780,19 +8784,19 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>81</v>
@@ -8801,15 +8805,15 @@
         <v>81</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8832,13 +8836,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8889,7 +8893,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8904,7 +8908,7 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
@@ -8916,24 +8920,24 @@
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8956,13 +8960,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9013,7 +9017,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9037,27 +9041,27 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9080,13 +9084,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9137,7 +9141,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9164,24 +9168,24 @@
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9204,13 +9208,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9261,7 +9265,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9288,7 +9292,7 @@
         <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>81</v>
@@ -9302,10 +9306,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9334,7 +9338,7 @@
         <v>138</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>140</v>
@@ -9375,19 +9379,19 @@
         <v>81</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9414,7 +9418,7 @@
         <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>81</v>
@@ -9428,10 +9432,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9454,16 +9458,16 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9513,7 +9517,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9522,7 +9526,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9554,10 +9558,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9583,13 +9587,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9615,13 +9619,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9639,7 +9643,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9680,10 +9684,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9709,13 +9713,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9765,7 +9769,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9792,7 +9796,7 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9806,10 +9810,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9832,16 +9836,16 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9891,7 +9895,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9906,13 +9910,13 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9932,10 +9936,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9958,13 +9962,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10015,7 +10019,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10042,13 +10046,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10056,10 +10060,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10082,13 +10086,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10139,7 +10143,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10163,10 +10167,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10175,15 +10179,15 @@
         <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10206,13 +10210,13 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10263,7 +10267,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10290,7 +10294,7 @@
         <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>81</v>
@@ -10304,10 +10308,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10336,7 +10340,7 @@
         <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>140</v>
@@ -10377,19 +10381,19 @@
         <v>81</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10416,7 +10420,7 @@
         <v>81</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>81</v>
@@ -10430,10 +10434,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10456,16 +10460,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10515,7 +10519,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10542,7 +10546,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10556,10 +10560,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10582,13 +10586,13 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10639,7 +10643,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10666,7 +10670,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10680,10 +10684,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10706,13 +10710,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10763,7 +10767,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10778,7 +10782,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10790,7 +10794,7 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10804,10 +10808,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10830,16 +10834,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10889,7 +10893,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10916,7 +10920,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10930,10 +10934,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10956,13 +10960,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11013,7 +11017,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11040,7 +11044,7 @@
         <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>81</v>
@@ -11054,10 +11058,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11086,7 +11090,7 @@
         <v>138</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>140</v>
@@ -11127,19 +11131,19 @@
         <v>81</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11166,7 +11170,7 @@
         <v>81</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>81</v>
@@ -11180,14 +11184,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11209,10 +11213,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11267,7 +11271,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11308,10 +11312,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11334,17 +11338,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11393,7 +11397,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11420,7 +11424,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11429,15 +11433,15 @@
         <v>81</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11460,17 +11464,17 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11519,7 +11523,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11534,19 +11538,19 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>81</v>
@@ -11555,15 +11559,15 @@
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11586,19 +11590,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11623,13 +11627,13 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11647,7 +11651,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11674,7 +11678,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11683,15 +11687,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11714,13 +11718,13 @@
         <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11771,7 +11775,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11786,10 +11790,10 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11798,7 +11802,7 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11807,15 +11811,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11838,19 +11842,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11899,7 +11903,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11926,7 +11930,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11940,10 +11944,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11966,16 +11970,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12001,13 +12005,13 @@
         <v>81</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12025,7 +12029,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12052,7 +12056,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12061,15 +12065,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12092,19 +12096,19 @@
         <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12129,13 +12133,13 @@
         <v>81</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12153,7 +12157,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12180,7 +12184,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12189,15 +12193,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12220,17 +12224,17 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12255,13 +12259,13 @@
         <v>81</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12279,7 +12283,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12306,7 +12310,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12315,15 +12319,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12346,19 +12350,19 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12383,13 +12387,13 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12407,7 +12411,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12434,7 +12438,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12443,15 +12447,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12474,13 +12478,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12531,7 +12535,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12567,15 +12571,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12598,13 +12602,13 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12655,7 +12659,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12682,7 +12686,7 @@
         <v>81</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>81</v>
@@ -12696,10 +12700,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12728,7 +12732,7 @@
         <v>138</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>140</v>
@@ -12769,19 +12773,19 @@
         <v>81</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12808,7 +12812,7 @@
         <v>81</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>81</v>
@@ -12822,10 +12826,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12848,17 +12852,17 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12883,13 +12887,13 @@
         <v>81</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12907,7 +12911,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12943,15 +12947,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12974,19 +12978,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13023,17 +13027,17 @@
         <v>81</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13060,7 +13064,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13069,18 +13073,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13102,19 +13106,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13163,7 +13167,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13172,10 +13176,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -13190,7 +13194,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13199,15 +13203,15 @@
         <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13230,13 +13234,13 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13287,7 +13291,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13314,7 +13318,7 @@
         <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>81</v>
@@ -13328,10 +13332,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13360,7 +13364,7 @@
         <v>138</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>140</v>
@@ -13401,19 +13405,19 @@
         <v>81</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13440,7 +13444,7 @@
         <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>81</v>
@@ -13454,10 +13458,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13480,19 +13484,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13541,7 +13545,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13556,19 +13560,19 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>81</v>
@@ -13577,15 +13581,15 @@
         <v>81</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13611,20 +13615,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13648,10 +13652,10 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13669,7 +13673,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13696,7 +13700,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13705,15 +13709,15 @@
         <v>81</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13736,17 +13740,17 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13795,7 +13799,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13810,19 +13814,19 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>81</v>
@@ -13831,15 +13835,15 @@
         <v>81</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13865,14 +13869,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13921,7 +13925,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13930,7 +13934,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13948,7 +13952,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13957,15 +13961,15 @@
         <v>81</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13991,16 +13995,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14029,7 +14033,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14047,7 +14051,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14062,19 +14066,19 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>81</v>
@@ -14083,15 +14087,15 @@
         <v>81</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14114,19 +14118,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14175,7 +14179,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14202,7 +14206,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14211,15 +14215,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14242,19 +14246,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14303,7 +14307,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14330,7 +14334,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14339,15 +14343,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14370,19 +14374,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14431,7 +14435,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14458,7 +14462,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14472,10 +14476,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14498,17 +14502,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14557,7 +14561,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14584,7 +14588,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14598,10 +14602,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14624,13 +14628,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14681,7 +14685,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14708,13 +14712,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14722,10 +14726,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14748,13 +14752,13 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14805,7 +14809,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -14832,7 +14836,7 @@
         <v>81</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>81</v>
@@ -14846,10 +14850,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14878,7 +14882,7 @@
         <v>138</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>140</v>
@@ -14931,7 +14935,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -14958,7 +14962,7 @@
         <v>81</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>81</v>
@@ -14972,14 +14976,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15001,10 +15005,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15059,7 +15063,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15100,10 +15104,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15126,13 +15130,13 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15183,7 +15187,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15210,7 +15214,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15224,10 +15228,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15250,13 +15254,13 @@
         <v>81</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15283,13 +15287,13 @@
         <v>81</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15307,7 +15311,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15334,24 +15338,24 @@
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15374,13 +15378,13 @@
         <v>81</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15407,13 +15411,13 @@
         <v>81</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15431,7 +15435,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15458,13 +15462,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15472,10 +15476,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15498,13 +15502,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15555,7 +15559,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15582,13 +15586,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15596,14 +15600,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15622,16 +15626,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15681,7 +15685,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15708,7 +15712,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15722,10 +15726,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15748,16 +15752,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15807,7 +15811,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15834,7 +15838,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -546,7 +546,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-MedicationDispenseRefill-869:if not null then fixed value #completed {null}MedicationDispenseRefill-819:if null then fixed value #in-progress {null}MedicationDispenseRefill-1555:if null then fixed value #in-progress {null}</t>
+mdr-24-869:52-52 &gt; 52.1-17: if not null then #completed {null}mdr-24-819:52-52 &gt; 52.1-17: if null then #in-progress {null}mdr-24-1555:52-31: if null then #in-progress {null}</t>
   </si>
   <si>
     <t>1555: fixed value = #in-progress when PRESCRIPTION - RELEASED DATE/TIME (52-31) case null</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="727">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -552,6 +552,9 @@
     <t>1555: fixed value = #in-progress when PRESCRIPTION - RELEASED DATE/TIME (52-31) case null</t>
   </si>
   <si>
+    <t>pharmacy.currentProvider,pharmacy.fill [m],pharmacy.fillsRemaining</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -833,6 +836,9 @@
 Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
+    <t>pharmacy.product [m]</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
@@ -1124,6 +1130,9 @@
   </si>
   <si>
     <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
+  </si>
+  <si>
+    <t>pharmacy.id,pharmacy.orderID,pharmacy.parent</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -1223,9 +1232,6 @@
     <t>824: source value from PRESCRIPTION - REFILL &gt; REFILL - QTY (52-52 &gt; 52.1-1)</t>
   </si>
   <si>
-    <t>Pharmacy: quantity</t>
-  </si>
-  <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
   </si>
   <si>
@@ -1336,9 +1342,6 @@
   </si>
   <si>
     <t>827: source value from PRESCRIPTION - REFILL &gt; REFILL - DAYS SUPPLY (52-52 &gt; 52.1-1.1)</t>
-  </si>
-  <si>
-    <t>Pharmacy: daysSupply</t>
   </si>
   <si>
     <t>effectiveUseTime</t>
@@ -1501,9 +1504,6 @@
     <t>836: source value from PRESCRIPTION - REFILL &gt; REFILL - MAIL/WINDOW/PARK (52-52 &gt; 52.1-2)</t>
   </si>
   <si>
-    <t>Pharmacy: routing</t>
-  </si>
-  <si>
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
@@ -1682,9 +1682,6 @@
     <t>1556: source value from PRESCRIPTION - SIG (52-10)</t>
   </si>
   <si>
-    <t>Pharmacy: sig</t>
-  </si>
-  <si>
     <t>RXO-6; RXE-21</t>
   </si>
   <si>
@@ -1731,6 +1728,9 @@
   </si>
   <si>
     <t>RxOut.RxOutpatSig.PatientInstructions</t>
+  </si>
+  <si>
+    <t>pharmacy.ptInstructions</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.timing</t>
@@ -2003,7 +2003,7 @@
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
   </si>
   <si>
-    <t>Pharmacy: dose.dose</t>
+    <t>pharmacy.dose [m]</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.comparator</t>
@@ -2022,9 +2022,6 @@
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.Unit</t>
-  </si>
-  <si>
-    <t>Pharmacy: dose.units</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.system</t>
@@ -2632,7 +2629,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="148.33203125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="64.80078125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -4264,19 +4261,19 @@
         <v>81</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AR13" t="s" s="2">
         <v>81</v>
@@ -4284,10 +4281,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4310,13 +4307,13 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4343,13 +4340,13 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
@@ -4367,7 +4364,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>82</v>
@@ -4391,10 +4388,10 @@
         <v>81</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>81</v>
@@ -4408,10 +4405,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4434,16 +4431,16 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4472,10 +4469,10 @@
         <v>115</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -4493,7 +4490,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -4520,7 +4517,7 @@
         <v>81</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>81</v>
@@ -4534,10 +4531,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4560,16 +4557,16 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4595,29 +4592,29 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>91</v>
@@ -4641,30 +4638,30 @@
         <v>81</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>81</v>
@@ -4686,16 +4683,16 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4721,13 +4718,13 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
@@ -4745,7 +4742,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>91</v>
@@ -4769,27 +4766,27 @@
         <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4812,13 +4809,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4869,7 +4866,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4896,7 +4893,7 @@
         <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>81</v>
@@ -4910,10 +4907,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4942,7 +4939,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>140</v>
@@ -4983,19 +4980,19 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -5022,7 +5019,7 @@
         <v>81</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>81</v>
@@ -5036,10 +5033,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5062,19 +5059,19 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -5123,7 +5120,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -5150,7 +5147,7 @@
         <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>81</v>
@@ -5159,15 +5156,15 @@
         <v>81</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5190,13 +5187,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5247,7 +5244,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5274,7 +5271,7 @@
         <v>81</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>81</v>
@@ -5288,10 +5285,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5320,7 +5317,7 @@
         <v>138</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>140</v>
@@ -5361,19 +5358,19 @@
         <v>81</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -5400,7 +5397,7 @@
         <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>81</v>
@@ -5414,10 +5411,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5443,16 +5440,16 @@
         <v>105</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -5462,7 +5459,7 @@
         <v>81</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>81</v>
@@ -5501,7 +5498,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5516,7 +5513,7 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
@@ -5528,7 +5525,7 @@
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>81</v>
@@ -5537,15 +5534,15 @@
         <v>81</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5568,16 +5565,16 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5627,7 +5624,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5654,7 +5651,7 @@
         <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>81</v>
@@ -5663,15 +5660,15 @@
         <v>81</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5697,14 +5694,14 @@
         <v>111</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5753,7 +5750,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5768,19 +5765,19 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -5789,15 +5786,15 @@
         <v>81</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5820,17 +5817,17 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5879,7 +5876,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5906,7 +5903,7 @@
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>81</v>
@@ -5915,15 +5912,15 @@
         <v>81</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5946,19 +5943,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -6007,7 +6004,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6034,7 +6031,7 @@
         <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>81</v>
@@ -6043,15 +6040,15 @@
         <v>81</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6074,19 +6071,19 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -6135,7 +6132,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6150,19 +6147,19 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>81</v>
@@ -6171,15 +6168,15 @@
         <v>81</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6202,16 +6199,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6261,7 +6258,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6276,36 +6273,36 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6328,13 +6325,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6385,7 +6382,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6409,10 +6406,10 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6426,10 +6423,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6452,13 +6449,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6509,7 +6506,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6536,10 +6533,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6550,10 +6547,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6576,13 +6573,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6633,7 +6630,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6657,10 +6654,10 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6674,10 +6671,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6700,13 +6697,13 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6757,7 +6754,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6784,7 +6781,7 @@
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>81</v>
@@ -6798,10 +6795,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6830,7 +6827,7 @@
         <v>138</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>140</v>
@@ -6883,7 +6880,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6910,7 +6907,7 @@
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>81</v>
@@ -6924,14 +6921,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6953,10 +6950,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -7011,7 +7008,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7052,10 +7049,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7078,17 +7075,17 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7113,13 +7110,13 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7137,7 +7134,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7164,7 +7161,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7178,10 +7175,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7204,13 +7201,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7261,7 +7258,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7276,19 +7273,19 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>81</v>
@@ -7302,10 +7299,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7328,13 +7325,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7385,7 +7382,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7400,19 +7397,19 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7426,10 +7423,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7452,16 +7449,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7511,7 +7508,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7526,36 +7523,36 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>81</v>
+        <v>359</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7578,13 +7575,13 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7596,46 +7593,46 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7650,7 +7647,7 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -7662,24 +7659,24 @@
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7702,13 +7699,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7759,7 +7756,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7786,24 +7783,24 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7826,13 +7823,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7883,7 +7880,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7910,7 +7907,7 @@
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>81</v>
@@ -7924,10 +7921,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7956,7 +7953,7 @@
         <v>138</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>140</v>
@@ -7997,19 +7994,19 @@
         <v>81</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8036,7 +8033,7 @@
         <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>81</v>
@@ -8050,10 +8047,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8076,19 +8073,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8137,7 +8134,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8152,19 +8149,19 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>387</v>
+        <v>172</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -8173,15 +8170,15 @@
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8207,20 +8204,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8244,10 +8241,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8265,7 +8262,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8292,7 +8289,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8301,15 +8298,15 @@
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8332,17 +8329,17 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8391,7 +8388,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8418,7 +8415,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8427,15 +8424,15 @@
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8461,14 +8458,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8517,7 +8514,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8526,7 +8523,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8544,7 +8541,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8553,15 +8550,15 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8587,16 +8584,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8645,7 +8642,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8672,7 +8669,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8681,15 +8678,15 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8712,13 +8709,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8769,7 +8766,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8784,19 +8781,19 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>425</v>
+        <v>172</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>81</v>
@@ -8805,15 +8802,15 @@
         <v>81</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8836,13 +8833,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8893,7 +8890,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8908,36 +8905,36 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8960,13 +8957,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9017,7 +9014,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9041,27 +9038,27 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9084,13 +9081,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9141,7 +9138,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9168,24 +9165,24 @@
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9208,13 +9205,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9265,7 +9262,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9292,7 +9289,7 @@
         <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>81</v>
@@ -9306,10 +9303,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9338,7 +9335,7 @@
         <v>138</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>140</v>
@@ -9379,19 +9376,19 @@
         <v>81</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9418,7 +9415,7 @@
         <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>81</v>
@@ -9432,10 +9429,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9458,16 +9455,16 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9517,7 +9514,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9526,7 +9523,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9558,10 +9555,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9587,13 +9584,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9619,13 +9616,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9643,7 +9640,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9684,10 +9681,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9713,13 +9710,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9769,7 +9766,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9796,7 +9793,7 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9810,10 +9807,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9836,16 +9833,16 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9895,7 +9892,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9910,13 +9907,13 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>476</v>
+        <v>172</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -10210,13 +10207,13 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10267,7 +10264,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10294,7 +10291,7 @@
         <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>81</v>
@@ -10340,7 +10337,7 @@
         <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>140</v>
@@ -10381,19 +10378,19 @@
         <v>81</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10420,7 +10417,7 @@
         <v>81</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>81</v>
@@ -10586,7 +10583,7 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>500</v>
@@ -10788,7 +10785,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -10960,13 +10957,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11017,7 +11014,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11044,7 +11041,7 @@
         <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>81</v>
@@ -11090,7 +11087,7 @@
         <v>138</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>140</v>
@@ -11131,19 +11128,19 @@
         <v>81</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11170,7 +11167,7 @@
         <v>81</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>81</v>
@@ -11191,7 +11188,7 @@
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11213,10 +11210,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11271,7 +11268,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11464,7 +11461,7 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>529</v>
@@ -11544,7 +11541,7 @@
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>534</v>
+        <v>81</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -11559,15 +11556,15 @@
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11590,19 +11587,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11627,31 +11624,31 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="Z72" t="s" s="2">
+      <c r="AA72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11687,15 +11684,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11718,13 +11715,13 @@
         <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11775,7 +11772,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11790,13 +11787,13 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="AL73" t="s" s="2">
+      <c r="AM73" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
@@ -11811,7 +11808,7 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="74" hidden="true">
@@ -12005,7 +12002,7 @@
         <v>81</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y75" t="s" s="2">
         <v>564</v>
@@ -12096,7 +12093,7 @@
         <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>570</v>
@@ -12133,7 +12130,7 @@
         <v>81</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y76" t="s" s="2">
         <v>574</v>
@@ -12224,7 +12221,7 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>580</v>
@@ -12259,7 +12256,7 @@
         <v>81</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y77" t="s" s="2">
         <v>583</v>
@@ -12350,7 +12347,7 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>589</v>
@@ -12387,7 +12384,7 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y78" t="s" s="2">
         <v>593</v>
@@ -12602,13 +12599,13 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12659,7 +12656,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12686,7 +12683,7 @@
         <v>81</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>81</v>
@@ -12732,7 +12729,7 @@
         <v>138</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>140</v>
@@ -12773,19 +12770,19 @@
         <v>81</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12812,7 +12809,7 @@
         <v>81</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>81</v>
@@ -12852,7 +12849,7 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L82" t="s" s="2">
         <v>607</v>
@@ -12887,7 +12884,7 @@
         <v>81</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y82" t="s" s="2">
         <v>610</v>
@@ -13027,14 +13024,14 @@
         <v>81</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>620</v>
@@ -13106,7 +13103,7 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L84" t="s" s="2">
         <v>624</v>
@@ -13234,13 +13231,13 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13291,7 +13288,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13318,7 +13315,7 @@
         <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>81</v>
@@ -13364,7 +13361,7 @@
         <v>138</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>140</v>
@@ -13405,19 +13402,19 @@
         <v>81</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13444,7 +13441,7 @@
         <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>81</v>
@@ -13484,19 +13481,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13545,7 +13542,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13572,7 +13569,7 @@
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>81</v>
@@ -13581,7 +13578,7 @@
         <v>81</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="88" hidden="true">
@@ -13615,20 +13612,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13652,10 +13649,10 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13673,7 +13670,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13700,7 +13697,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13709,7 +13706,7 @@
         <v>81</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="89" hidden="true">
@@ -13740,17 +13737,17 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13799,7 +13796,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13820,13 +13817,13 @@
         <v>645</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>81</v>
@@ -13835,15 +13832,15 @@
         <v>81</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13869,14 +13866,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13925,7 +13922,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13934,7 +13931,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13952,7 +13949,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13961,15 +13958,15 @@
         <v>81</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13995,16 +13992,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14033,7 +14030,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14051,7 +14048,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14066,19 +14063,19 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>645</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>81</v>
@@ -14087,15 +14084,15 @@
         <v>81</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14118,19 +14115,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14179,7 +14176,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14206,24 +14203,24 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR92" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR92" t="s" s="2">
-        <v>661</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14246,19 +14243,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14307,7 +14304,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14334,24 +14331,24 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR93" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR93" t="s" s="2">
-        <v>670</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14374,19 +14371,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14435,7 +14432,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14462,7 +14459,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14476,10 +14473,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14502,17 +14499,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14561,7 +14558,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14588,7 +14585,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14602,10 +14599,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14628,13 +14625,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14685,7 +14682,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14712,13 +14709,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ96" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ96" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14726,10 +14723,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14752,13 +14749,13 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14809,7 +14806,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -14836,7 +14833,7 @@
         <v>81</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>81</v>
@@ -14850,10 +14847,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14882,7 +14879,7 @@
         <v>138</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>140</v>
@@ -14935,7 +14932,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -14962,7 +14959,7 @@
         <v>81</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>81</v>
@@ -14976,14 +14973,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15005,10 +15002,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15063,7 +15060,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15104,10 +15101,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15130,13 +15127,13 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15187,7 +15184,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15214,7 +15211,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15228,10 +15225,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15254,13 +15251,13 @@
         <v>81</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15287,14 +15284,14 @@
         <v>81</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y101" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="Z101" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="Z101" t="s" s="2">
-        <v>699</v>
-      </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
       </c>
@@ -15311,7 +15308,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15338,24 +15335,24 @@
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AR101" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="AR101" t="s" s="2">
-        <v>701</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15378,13 +15375,13 @@
         <v>81</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15411,14 +15408,14 @@
         <v>81</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y102" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="Z102" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="Z102" t="s" s="2">
-        <v>706</v>
-      </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
       </c>
@@ -15435,7 +15432,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15462,13 +15459,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
         <v>707</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>708</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15476,10 +15473,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15502,13 +15499,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>710</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>712</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15559,7 +15556,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15586,13 +15583,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ103" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15600,14 +15597,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15626,16 +15623,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15685,7 +15682,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15712,7 +15709,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15726,10 +15723,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15752,16 +15749,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>724</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15811,7 +15808,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15838,7 +15835,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="726">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -552,7 +552,7 @@
     <t>1555: fixed value = #in-progress when PRESCRIPTION - RELEASED DATE/TIME (52-31) case null</t>
   </si>
   <si>
-    <t>pharmacy.currentProvider,pharmacy.fill [m],pharmacy.fillsRemaining</t>
+    <t>pharmacy (med).fill [m],med.fill [m]</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -836,7 +836,7 @@
 Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
-    <t>pharmacy.product [m]</t>
+    <t>pharmacy (med).route,med.route</t>
   </si>
   <si>
     <t>./code</t>
@@ -956,6 +956,9 @@
     <t>RxOut.ActivityLog.PatientIEN,RxOut.ActivityLogOtherComments.PatientIEN,RxOut.RxOutpat.PatientIEN,RxOut.RxOutpatExt.PatientIEN,RxOut.RxOutpatExt.PatientSID,RxOut.RxOutpatFill.PatientIEN,RxOut.RxOutpatMedInstructions.PatientIEN,RxOut.RxOutpatSig.PatientIEN</t>
   </si>
   <si>
+    <t>pharmacy (med).units,med.units</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1130,9 +1133,6 @@
   </si>
   <si>
     <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
-  </si>
-  <si>
-    <t>pharmacy.id,pharmacy.orderID,pharmacy.parent</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -1730,9 +1730,6 @@
     <t>RxOut.RxOutpatSig.PatientInstructions</t>
   </si>
   <si>
-    <t>pharmacy.ptInstructions</t>
-  </si>
-  <si>
     <t>MedicationDispense.dosageInstruction.timing</t>
   </si>
   <si>
@@ -2003,7 +2000,7 @@
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
   </si>
   <si>
-    <t>pharmacy.dose [m]</t>
+    <t>pharmacy (med).dose [m],med.dose [m]</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.comparator</t>
@@ -2629,7 +2626,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="148.33203125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="64.80078125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -6279,30 +6276,30 @@
         <v>302</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>81</v>
+        <v>303</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6325,13 +6322,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6382,7 +6379,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6406,10 +6403,10 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6423,10 +6420,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6449,13 +6446,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6506,7 +6503,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6533,10 +6530,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6547,10 +6544,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6573,13 +6570,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6630,7 +6627,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6654,10 +6651,10 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6671,10 +6668,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6795,10 +6792,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6921,14 +6918,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6950,10 +6947,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -7008,7 +7005,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7049,10 +7046,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7078,14 +7075,14 @@
         <v>187</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7113,10 +7110,10 @@
         <v>181</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7134,7 +7131,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7161,7 +7158,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7175,10 +7172,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7201,13 +7198,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7258,7 +7255,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7273,7 +7270,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -7282,10 +7279,10 @@
         <v>172</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>81</v>
@@ -7299,10 +7296,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7325,13 +7322,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7382,7 +7379,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7397,7 +7394,7 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -7409,7 +7406,7 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7423,10 +7420,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7449,16 +7446,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7508,7 +7505,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7523,13 +7520,13 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>359</v>
+        <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>360</v>
@@ -11188,7 +11185,7 @@
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11210,10 +11207,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11268,7 +11265,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11793,7 +11790,7 @@
         <v>549</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>550</v>
+        <v>81</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
@@ -11813,10 +11810,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11839,19 +11836,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11900,7 +11897,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11927,7 +11924,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11941,10 +11938,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11967,16 +11964,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12005,28 +12002,28 @@
         <v>181</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="Z75" t="s" s="2">
+      <c r="AA75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12053,24 +12050,24 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR75" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>568</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12096,16 +12093,16 @@
         <v>187</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12133,28 +12130,28 @@
         <v>181</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="Z76" t="s" s="2">
+      <c r="AA76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12181,24 +12178,24 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR76" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR76" t="s" s="2">
-        <v>578</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12224,14 +12221,14 @@
         <v>187</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12259,28 +12256,28 @@
         <v>181</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="Z77" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="Z77" t="s" s="2">
+      <c r="AA77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12307,24 +12304,24 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR77" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR77" t="s" s="2">
-        <v>587</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12350,16 +12347,16 @@
         <v>187</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12387,28 +12384,28 @@
         <v>181</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="Z78" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="Z78" t="s" s="2">
+      <c r="AA78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12435,24 +12432,24 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR78" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR78" t="s" s="2">
-        <v>597</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12475,13 +12472,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12532,7 +12529,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12568,15 +12565,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12697,10 +12694,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12823,10 +12820,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12852,14 +12849,14 @@
         <v>187</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12887,28 +12884,28 @@
         <v>181</v>
       </c>
       <c r="Y82" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="Z82" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="Z82" t="s" s="2">
+      <c r="AA82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12944,15 +12941,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12975,19 +12972,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13034,7 +13031,7 @@
         <v>202</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13061,7 +13058,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13070,18 +13067,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C84" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13106,16 +13103,16 @@
         <v>374</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="N84" t="s" s="2">
-        <v>626</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13164,7 +13161,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13173,42 +13170,42 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="AJ84" t="s" s="2">
+      <c r="AK84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="AK84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO84" t="s" s="2">
+      <c r="AP84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR84" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR84" t="s" s="2">
-        <v>630</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13329,10 +13326,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13455,10 +13452,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13557,13 +13554,13 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AL87" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="AL87" t="s" s="2">
+      <c r="AM87" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -13583,10 +13580,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13711,10 +13708,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13811,13 +13808,13 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AL89" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="AL89" t="s" s="2">
-        <v>645</v>
-      </c>
       <c r="AM89" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -13837,10 +13834,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13963,10 +13960,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14030,7 +14027,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14063,13 +14060,13 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -14089,10 +14086,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14115,19 +14112,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14176,7 +14173,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14203,24 +14200,24 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR92" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR92" t="s" s="2">
-        <v>660</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14243,19 +14240,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14304,7 +14301,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14331,24 +14328,24 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR93" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR93" t="s" s="2">
-        <v>669</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14374,16 +14371,16 @@
         <v>374</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14432,7 +14429,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14459,7 +14456,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14473,10 +14470,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14502,14 +14499,14 @@
         <v>374</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>679</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14558,7 +14555,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14585,7 +14582,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14599,10 +14596,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14625,13 +14622,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>683</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>684</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14682,7 +14679,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14709,13 +14706,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ96" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ96" t="s" s="2">
-        <v>686</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14723,10 +14720,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14847,10 +14844,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14973,14 +14970,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15002,10 +14999,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15060,7 +15057,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15101,10 +15098,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15130,10 +15127,10 @@
         <v>277</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>691</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>692</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15184,7 +15181,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15211,7 +15208,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15225,10 +15222,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15254,10 +15251,10 @@
         <v>187</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15287,11 +15284,11 @@
         <v>181</v>
       </c>
       <c r="Y101" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="Z101" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="Z101" t="s" s="2">
-        <v>698</v>
-      </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
       </c>
@@ -15308,7 +15305,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15341,18 +15338,18 @@
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="AR101" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="AR101" t="s" s="2">
-        <v>700</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15378,10 +15375,10 @@
         <v>187</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15411,11 +15408,11 @@
         <v>181</v>
       </c>
       <c r="Y102" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="Z102" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="Z102" t="s" s="2">
-        <v>705</v>
-      </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
       </c>
@@ -15432,7 +15429,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15459,13 +15456,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15473,10 +15470,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15499,13 +15496,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15556,7 +15553,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15583,13 +15580,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ103" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15597,14 +15594,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15623,16 +15620,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15682,7 +15679,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15709,7 +15706,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15723,10 +15720,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15749,16 +15746,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>722</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15808,7 +15805,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15835,7 +15832,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -2626,7 +2626,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="148.33203125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="728">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -552,7 +552,7 @@
     <t>1555: fixed value = #in-progress when PRESCRIPTION - RELEASED DATE/TIME (52-31) case null</t>
   </si>
   <si>
-    <t>pharmacy (med).fill [m],med.fill [m]</t>
+    <t>Medication.RefillNumber,Medication.EBilling,Medication.Fills,Medication.LastFilled</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -836,7 +836,8 @@
 Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
-    <t>pharmacy (med).route,med.route</t>
+    <t>Medication.DrugProduct,Medication.CMOP
+Medication.DrugProduct.Identifier2,Medication.DrugProduct.ProductName,Medication.DrugProductExtension.FederalSchedule</t>
   </si>
   <si>
     <t>./code</t>
@@ -928,6 +929,10 @@
 Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
   </si>
   <si>
+    <t>Medication.DrugProduct,Medication.CMOP
+Medication.DrugProduct.Description,Medication.DrugProduct.OriginalText,Medication.DrugProduct.Description,Medication.DrugProduct.OriginalText,Medication.ATCCode.Code,Medication.Generic.Description,Medication.Route.Description,Medication.OrderCategory.Description,Medication.OriginalText,Medication.OriginalText</t>
+  </si>
+  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
@@ -956,9 +961,6 @@
     <t>RxOut.ActivityLog.PatientIEN,RxOut.ActivityLogOtherComments.PatientIEN,RxOut.RxOutpat.PatientIEN,RxOut.RxOutpatExt.PatientIEN,RxOut.RxOutpatExt.PatientSID,RxOut.RxOutpatFill.PatientIEN,RxOut.RxOutpatMedInstructions.PatientIEN,RxOut.RxOutpatSig.PatientIEN</t>
   </si>
   <si>
-    <t>pharmacy (med).units,med.units</t>
-  </si>
-  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1133,6 +1135,9 @@
   </si>
   <si>
     <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
+  </si>
+  <si>
+    <t>Medication.ExternalId,Medication.PlacerId</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -1730,6 +1735,9 @@
     <t>RxOut.RxOutpatSig.PatientInstructions</t>
   </si>
   <si>
+    <t>Medication.TextInstruction</t>
+  </si>
+  <si>
     <t>MedicationDispense.dosageInstruction.timing</t>
   </si>
   <si>
@@ -2000,7 +2008,7 @@
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
   </si>
   <si>
-    <t>pharmacy (med).dose [m],med.dose [m]</t>
+    <t>Medication.DosageSteps,Medication.Route,Medication.DoseQuantity,Medication.DoseUoM,Medication.Duration,Medication.Frequency,Medication.TextInstruction,Medication.Conjunction,Medication.Noun,Medication.UnitsPerDose,Medication.Verb</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.comparator</t>
@@ -2626,7 +2634,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="148.33203125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -6150,13 +6158,13 @@
         <v>293</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>81</v>
@@ -6165,15 +6173,15 @@
         <v>81</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6196,16 +6204,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6255,7 +6263,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6270,13 +6278,13 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>303</v>
+        <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>304</v>
@@ -7526,30 +7534,30 @@
         <v>359</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>81</v>
+        <v>360</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7575,10 +7583,10 @@
         <v>187</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7590,7 +7598,7 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>81</v>
@@ -7608,10 +7616,10 @@
         <v>181</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -7629,7 +7637,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7644,7 +7652,7 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -7656,24 +7664,24 @@
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7696,13 +7704,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7753,7 +7761,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7780,24 +7788,24 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7918,10 +7926,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8044,10 +8052,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8070,19 +8078,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8131,7 +8139,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8146,7 +8154,7 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
@@ -8158,7 +8166,7 @@
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -8167,15 +8175,15 @@
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8201,20 +8209,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8238,10 +8246,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8259,7 +8267,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8286,7 +8294,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8295,15 +8303,15 @@
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8329,14 +8337,14 @@
         <v>212</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8385,7 +8393,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8412,7 +8420,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8421,15 +8429,15 @@
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8455,14 +8463,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8511,7 +8519,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8520,7 +8528,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8538,7 +8546,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8547,15 +8555,15 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8581,16 +8589,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8639,7 +8647,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8666,7 +8674,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8675,15 +8683,15 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8706,13 +8714,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8763,7 +8771,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8778,7 +8786,7 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
@@ -8790,7 +8798,7 @@
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>81</v>
@@ -8799,15 +8807,15 @@
         <v>81</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8830,13 +8838,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8887,7 +8895,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8902,7 +8910,7 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
@@ -8914,24 +8922,24 @@
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8954,13 +8962,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9011,7 +9019,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9035,27 +9043,27 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9078,13 +9086,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9135,7 +9143,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9162,24 +9170,24 @@
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9300,10 +9308,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9426,10 +9434,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9455,13 +9463,13 @@
         <v>212</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9511,7 +9519,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9520,7 +9528,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9552,10 +9560,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9581,13 +9589,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9613,13 +9621,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9637,7 +9645,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9678,10 +9686,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9707,13 +9715,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9763,7 +9771,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9790,7 +9798,7 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9804,10 +9812,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9833,13 +9841,13 @@
         <v>212</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9889,7 +9897,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9904,7 +9912,7 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
@@ -9930,10 +9938,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9956,13 +9964,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10013,7 +10021,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10040,13 +10048,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10054,10 +10062,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10080,13 +10088,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10137,7 +10145,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10161,10 +10169,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10173,15 +10181,15 @@
         <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10302,10 +10310,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10428,10 +10436,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10454,16 +10462,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10513,7 +10521,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10540,7 +10548,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10554,10 +10562,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10580,13 +10588,13 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10637,7 +10645,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10664,7 +10672,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10678,10 +10686,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10704,13 +10712,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10761,7 +10769,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10776,7 +10784,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10788,7 +10796,7 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10802,10 +10810,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10828,16 +10836,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10887,7 +10895,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10914,7 +10922,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10928,10 +10936,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11052,10 +11060,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11178,10 +11186,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11306,10 +11314,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11332,17 +11340,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11391,7 +11399,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11418,7 +11426,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11427,15 +11435,15 @@
         <v>81</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11461,14 +11469,14 @@
         <v>212</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11517,7 +11525,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11532,7 +11540,7 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
@@ -11544,7 +11552,7 @@
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>81</v>
@@ -11553,15 +11561,15 @@
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11587,16 +11595,16 @@
         <v>187</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11624,10 +11632,10 @@
         <v>181</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11645,7 +11653,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11672,7 +11680,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11681,15 +11689,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11715,10 +11723,10 @@
         <v>212</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11769,7 +11777,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11784,19 +11792,19 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>81</v>
+        <v>551</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11805,15 +11813,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11836,19 +11844,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11897,7 +11905,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11924,7 +11932,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11938,10 +11946,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11964,16 +11972,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12002,10 +12010,10 @@
         <v>181</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12023,7 +12031,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12050,7 +12058,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12059,15 +12067,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12093,16 +12101,16 @@
         <v>187</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12130,10 +12138,10 @@
         <v>181</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12151,7 +12159,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12178,7 +12186,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12187,15 +12195,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12221,14 +12229,14 @@
         <v>187</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12256,10 +12264,10 @@
         <v>181</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12277,7 +12285,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12304,7 +12312,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12313,15 +12321,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12347,16 +12355,16 @@
         <v>187</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12384,10 +12392,10 @@
         <v>181</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12405,7 +12413,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12432,7 +12440,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12441,15 +12449,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12472,13 +12480,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12529,7 +12537,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12565,15 +12573,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12694,10 +12702,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12820,10 +12828,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12849,14 +12857,14 @@
         <v>187</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12884,10 +12892,10 @@
         <v>181</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12905,7 +12913,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12941,15 +12949,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12972,19 +12980,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13031,7 +13039,7 @@
         <v>202</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13058,7 +13066,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13067,18 +13075,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13100,19 +13108,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13161,7 +13169,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13170,10 +13178,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -13188,7 +13196,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13197,15 +13205,15 @@
         <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13326,10 +13334,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13452,10 +13460,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13478,19 +13486,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13539,7 +13547,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13554,19 +13562,19 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>81</v>
@@ -13575,15 +13583,15 @@
         <v>81</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13609,20 +13617,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13646,10 +13654,10 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13667,7 +13675,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13694,7 +13702,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13703,15 +13711,15 @@
         <v>81</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13737,14 +13745,14 @@
         <v>212</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13793,7 +13801,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13808,19 +13816,19 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>81</v>
@@ -13829,15 +13837,15 @@
         <v>81</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13863,14 +13871,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13919,7 +13927,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13928,7 +13936,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13946,7 +13954,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13955,15 +13963,15 @@
         <v>81</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13989,16 +13997,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14027,7 +14035,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14045,7 +14053,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14060,19 +14068,19 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>81</v>
@@ -14081,15 +14089,15 @@
         <v>81</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14112,19 +14120,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14173,7 +14181,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14200,7 +14208,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14209,15 +14217,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14240,19 +14248,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14301,7 +14309,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14328,7 +14336,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14337,15 +14345,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14368,19 +14376,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14429,7 +14437,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14456,7 +14464,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14470,10 +14478,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14496,17 +14504,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14555,7 +14563,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14582,7 +14590,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14596,10 +14604,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14625,10 +14633,10 @@
         <v>321</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14679,7 +14687,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14706,13 +14714,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14720,10 +14728,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14844,10 +14852,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14970,10 +14978,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15098,10 +15106,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15127,10 +15135,10 @@
         <v>277</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15181,7 +15189,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15208,7 +15216,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15222,10 +15230,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15251,10 +15259,10 @@
         <v>187</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15284,10 +15292,10 @@
         <v>181</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15305,7 +15313,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15332,24 +15340,24 @@
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15375,10 +15383,10 @@
         <v>187</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15408,10 +15416,10 @@
         <v>181</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15429,7 +15437,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15456,13 +15464,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15470,10 +15478,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15496,13 +15504,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15553,7 +15561,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15580,13 +15588,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15594,14 +15602,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15620,16 +15628,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15679,7 +15687,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15706,7 +15714,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15720,10 +15728,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15746,16 +15754,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15805,7 +15813,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15832,7 +15840,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -837,7 +837,7 @@
   </si>
   <si>
     <t>Medication.DrugProduct,Medication.CMOP
-Medication.DrugProduct.Identifier2,Medication.DrugProduct.ProductName,Medication.DrugProductExtension.FederalSchedule</t>
+Medication.DrugProduct.Identifier2,Medication.DrugProduct.ProductName,Medication.Extension[DrugProductExtension].FederalSchedule</t>
   </si>
   <si>
     <t>./code</t>
@@ -930,7 +930,7 @@
   </si>
   <si>
     <t>Medication.DrugProduct,Medication.CMOP
-Medication.DrugProduct.Description,Medication.DrugProduct.OriginalText,Medication.DrugProduct.Description,Medication.DrugProduct.OriginalText,Medication.ATCCode.Code,Medication.Generic.Description,Medication.Route.Description,Medication.OrderCategory.Description,Medication.OriginalText,Medication.OriginalText</t>
+Medication.ComponentMeds[DrugProduct].Description,Medication.ComponentMeds[DrugProduct].OriginalText,Medication.DrugProduct.Description,Medication.DrugProduct.OriginalText,Medication.ATCCode.Code,Medication.Generic.Description,Medication.Route.Description,Medication.OrderCategory.Description,Medication.OriginalText,Medication.OriginalText</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION (52) to MedicationDispense</t>
+    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION (52) to MedicationDispense.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="721">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1959,29 +1959,6 @@
   </si>
   <si>
     <t>doseQuantity</t>
-  </si>
-  <si>
-    <t>A fixed quantity (no comparator)</t>
-  </si>
-  <si>
-    <t>The comparator is not used on a SimpleQuantity</t>
-  </si>
-  <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.id</t>
@@ -13105,19 +13082,19 @@
         <v>81</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>375</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="O84" t="s" s="2">
         <v>620</v>
@@ -13178,10 +13155,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>628</v>
+        <v>81</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>629</v>
+        <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -13196,7 +13173,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>630</v>
+        <v>597</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13205,15 +13182,15 @@
         <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>631</v>
+        <v>622</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13334,10 +13311,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13460,10 +13437,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13562,13 +13539,13 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -13588,10 +13565,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13716,10 +13693,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13816,13 +13793,13 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -13842,10 +13819,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13968,10 +13945,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14035,7 +14012,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14068,13 +14045,13 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -14094,10 +14071,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14120,19 +14097,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14181,7 +14158,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14208,7 +14185,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14217,15 +14194,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>661</v>
+        <v>654</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14248,19 +14225,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14309,7 +14286,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14336,7 +14313,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14345,15 +14322,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>670</v>
+        <v>663</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14379,16 +14356,16 @@
         <v>375</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14437,7 +14414,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14464,7 +14441,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14478,10 +14455,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14507,14 +14484,14 @@
         <v>375</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14563,7 +14540,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14590,7 +14567,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14604,10 +14581,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14633,10 +14610,10 @@
         <v>321</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14687,7 +14664,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14714,13 +14691,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14728,10 +14705,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14852,10 +14829,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14978,10 +14955,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15106,10 +15083,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15135,10 +15112,10 @@
         <v>277</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15189,7 +15166,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15216,7 +15193,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15230,10 +15207,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15259,10 +15236,10 @@
         <v>187</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15292,10 +15269,10 @@
         <v>181</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15313,7 +15290,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15346,18 +15323,18 @@
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>701</v>
+        <v>694</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15383,10 +15360,10 @@
         <v>187</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15416,10 +15393,10 @@
         <v>181</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15437,7 +15414,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15464,13 +15441,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15478,10 +15455,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15504,13 +15481,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15561,7 +15538,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15588,13 +15565,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15602,14 +15579,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15628,16 +15605,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15687,7 +15664,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15714,7 +15691,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15728,10 +15705,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15754,16 +15731,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15813,7 +15790,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15840,7 +15817,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="722">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -546,10 +546,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mdr-24-869:52-52 &gt; 52.1-17: if not null then #completed {null}mdr-24-819:52-52 &gt; 52.1-17: if null then #in-progress {null}mdr-24-1555:52-31: if null then #in-progress {null}</t>
-  </si>
-  <si>
-    <t>1555: fixed value = #in-progress when PRESCRIPTION - RELEASED DATE/TIME (52-31) case null</t>
+mdr-24-869:If (52-52 &gt; 52.1-17) is not null then fixed value #completed {null}mdr-24-819:If (52-52 &gt; 52.1-17) is null then fixed value #in-progress {null}mdr-24-1555:If (52-31) is null then fixed value #in-progress {null}</t>
+  </si>
+  <si>
+    <t>1555: fixed value = #in-progress when PRESCRIPTION - RELEASED DATE/TIME (52-31) if null</t>
   </si>
   <si>
     <t>Medication.RefillNumber,Medication.EBilling,Medication.Fills,Medication.LastFilled</t>
@@ -829,7 +829,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1561: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (52-6 &gt; 50-22)</t>
+    <t>1561: source value based on PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (52-6 &gt; 50-22)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.LocalDrugIEN,RxOut.RxOutpat.NationalDrugIEN,RxOut.RxOutpatFill.LocalDrugIEN,RxOut.RxOutpatFill.NationalDrugIEN
@@ -922,7 +922,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1560: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (52-6 &gt; 50-.01)</t>
+    <t>1560: source value based on PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (52-6 &gt; 50-.01)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.LocalDrugIEN,RxOut.RxOutpat.NationalDrugIEN,RxOut.RxOutpatFill.LocalDrugIEN,RxOut.RxOutpatFill.NationalDrugIEN
@@ -955,7 +955,7 @@
     <t>SubstanceAdministration-&gt;subject-&gt;Patient.</t>
   </si>
   <si>
-    <t>1551: reference from PRESCRIPTION - PATIENT (52-2)</t>
+    <t>1551: reference based on PRESCRIPTION - PATIENT (52-2)</t>
   </si>
   <si>
     <t>RxOut.ActivityLog.PatientIEN,RxOut.ActivityLogOtherComments.PatientIEN,RxOut.RxOutpat.PatientIEN,RxOut.RxOutpatExt.PatientIEN,RxOut.RxOutpatExt.PatientSID,RxOut.RxOutpatFill.PatientIEN,RxOut.RxOutpatMedInstructions.PatientIEN,RxOut.RxOutpatSig.PatientIEN</t>
@@ -1087,7 +1087,7 @@
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
-    <t>1728: reference from PRESCRIPTION - REFILL &gt; REFILL - PHARMACIST NAME (52-52 &gt; 52.1-4)</t>
+    <t>1728: reference based on PRESCRIPTION - REFILL &gt; REFILL - PHARMACIST NAME (52-52 &gt; 52.1-4)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1109,7 +1109,7 @@
     <t>The principal physical location where the dispense was performed.</t>
   </si>
   <si>
-    <t>1715: reference from PRESCRIPTION - REFILL &gt; REFILL - DIVISION &gt; OUTPATIENT SITE - DEFAULT ERX CLINIC (52-52 &gt; 52.1-8 &gt; 59-10)</t>
+    <t>1715: reference based on PRESCRIPTION - REFILL &gt; REFILL - DIVISION &gt; OUTPATIENT SITE - DEFAULT ERX CLINIC (52-52 &gt; 52.1-8 &gt; 59-10)</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role</t>
@@ -1131,7 +1131,7 @@
     <t>Maps to basedOn in Event logical model.</t>
   </si>
   <si>
-    <t>1553: reference from PRESCRIPTION - PLACER ORDER # (52-39.3)</t>
+    <t>1553: reference based on PRESCRIPTION - PLACER ORDER # (52-39.3)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
@@ -1234,7 +1234,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>824: source value from PRESCRIPTION - REFILL &gt; REFILL - QTY (52-52 &gt; 52.1-1)</t>
+    <t>824: source value based on PRESCRIPTION - REFILL &gt; REFILL - QTY (52-52 &gt; 52.1-1)</t>
   </si>
   <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
@@ -1346,7 +1346,7 @@
     <t>The amount of medication expressed as a timing amount.</t>
   </si>
   <si>
-    <t>827: source value from PRESCRIPTION - REFILL &gt; REFILL - DAYS SUPPLY (52-52 &gt; 52.1-1.1)</t>
+    <t>827: source value based on PRESCRIPTION - REFILL &gt; REFILL - DAYS SUPPLY (52-52 &gt; 52.1-1.1)</t>
   </si>
   <si>
     <t>effectiveUseTime</t>
@@ -1371,7 +1371,7 @@
     <t>The time when the dispensed product was packaged and reviewed.</t>
   </si>
   <si>
-    <t>833: source value from PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (52-52 &gt; 52.1-17)</t>
+    <t>833: source value based on PRESCRIPTION - REFILL &gt; REFILL - RELEASED DATE/TIME (52-52 &gt; 52.1-17)</t>
   </si>
   <si>
     <t>.effectiveTime[xmi:type=IVL_TS].low</t>
@@ -1506,7 +1506,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>836: source value from PRESCRIPTION - REFILL &gt; REFILL - MAIL/WINDOW/PARK (52-52 &gt; 52.1-2)</t>
+    <t>836: source value based on PRESCRIPTION - REFILL &gt; REFILL - MAIL/WINDOW/PARK (52-52 &gt; 52.1-2)</t>
   </si>
   <si>
     <t>MedicationDispense.receiver</t>
@@ -1609,7 +1609,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>1718: source value from PRESCRIPTION - REFILL &gt; REFILL - REMARKS (52-52 &gt; 52.1-3)</t>
+    <t>1718: source value based on PRESCRIPTION - REFILL &gt; REFILL - REMARKS (52-52 &gt; 52.1-3)</t>
   </si>
   <si>
     <t>Act.text</t>
@@ -1684,7 +1684,7 @@
     <t>Dosage.text</t>
   </si>
   <si>
-    <t>1556: source value from PRESCRIPTION - SIG (52-10)</t>
+    <t>1556: source value based on PRESCRIPTION - SIG (52-10)</t>
   </si>
   <si>
     <t>RXO-6; RXE-21</t>
@@ -1729,7 +1729,7 @@
     <t>Dosage.patientInstruction</t>
   </si>
   <si>
-    <t>1557: source value from PRESCRIPTION - PATIENT INSTRUCTIONS (52-114)</t>
+    <t>1557: source value based on PRESCRIPTION - PATIENT INSTRUCTIONS (52-114)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatSig.PatientInstructions</t>
@@ -1979,7 +1979,11 @@
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].value</t>
   </si>
   <si>
-    <t>1558: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (52-113 &gt; 52.0113-.01) case number</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+mdr-24-1558:If number then source value from (52-113 &gt; 52.0113-.01) {null}</t>
+  </si>
+  <si>
+    <t>1558: source value based on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (52-113 &gt; 52.0113-.01) if number</t>
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
@@ -2000,7 +2004,7 @@
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].unit</t>
   </si>
   <si>
-    <t>1559: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (52-113 &gt; 52.0113-2)</t>
+    <t>1559: source value based on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (52-113 &gt; 52.0113-2)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.Unit</t>
@@ -2609,7 +2613,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="148.33203125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="149.3671875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
@@ -13536,16 +13540,16 @@
         <v>81</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>103</v>
+        <v>631</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -13565,10 +13569,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13693,10 +13697,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13793,13 +13797,13 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -13819,10 +13823,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13945,10 +13949,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14012,7 +14016,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14045,13 +14049,13 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -14071,10 +14075,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14097,19 +14101,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14158,7 +14162,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14185,7 +14189,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14194,15 +14198,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14225,19 +14229,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14286,7 +14290,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14313,7 +14317,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14322,15 +14326,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14356,16 +14360,16 @@
         <v>375</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14414,7 +14418,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14441,7 +14445,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14455,10 +14459,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14484,14 +14488,14 @@
         <v>375</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14540,7 +14544,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14567,7 +14571,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14581,10 +14585,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14610,10 +14614,10 @@
         <v>321</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14664,7 +14668,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14691,13 +14695,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14705,10 +14709,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14829,10 +14833,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14955,10 +14959,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15083,10 +15087,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15112,10 +15116,10 @@
         <v>277</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15166,7 +15170,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15193,7 +15197,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15207,10 +15211,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15236,10 +15240,10 @@
         <v>187</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15269,10 +15273,10 @@
         <v>181</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15290,7 +15294,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15323,18 +15327,18 @@
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15360,10 +15364,10 @@
         <v>187</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15393,10 +15397,10 @@
         <v>181</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15414,7 +15418,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15441,13 +15445,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15455,10 +15459,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15481,13 +15485,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15538,7 +15542,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15565,13 +15569,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15579,14 +15583,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15605,16 +15609,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15664,7 +15668,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15691,7 +15695,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15705,10 +15709,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15731,16 +15735,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15790,7 +15794,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15817,7 +15821,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4228" uniqueCount="723">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2020,6 +2020,9 @@
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].code</t>
+  </si>
+  <si>
+    <t>see mapping [VF_DoseUnits](ConceptMap-VF-DoseUnits.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/DoseUnits</t>
@@ -14014,9 +14017,11 @@
       <c r="X91" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="Y91" s="2"/>
+      <c r="Y91" t="s" s="2">
+        <v>645</v>
+      </c>
       <c r="Z91" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14049,7 +14054,7 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>640</v>
@@ -14075,10 +14080,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14101,19 +14106,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14162,7 +14167,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14189,7 +14194,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14198,15 +14203,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14229,19 +14234,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14290,7 +14295,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14317,7 +14322,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14326,15 +14331,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14360,16 +14365,16 @@
         <v>375</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14418,7 +14423,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14445,7 +14450,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14459,10 +14464,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14488,14 +14493,14 @@
         <v>375</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14544,7 +14549,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14571,7 +14576,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14585,10 +14590,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14614,10 +14619,10 @@
         <v>321</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14668,7 +14673,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14695,13 +14700,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14709,10 +14714,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14833,10 +14838,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14959,10 +14964,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15087,10 +15092,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15116,10 +15121,10 @@
         <v>277</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15170,7 +15175,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15197,7 +15202,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15211,10 +15216,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15240,10 +15245,10 @@
         <v>187</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15273,10 +15278,10 @@
         <v>181</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15294,7 +15299,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15327,18 +15332,18 @@
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15364,10 +15369,10 @@
         <v>187</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15397,10 +15402,10 @@
         <v>181</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15418,7 +15423,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15445,13 +15450,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15459,10 +15464,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15485,13 +15490,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15542,7 +15547,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15569,13 +15574,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15583,14 +15588,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15609,16 +15614,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15668,7 +15673,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15695,7 +15700,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15709,10 +15714,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15735,16 +15740,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15794,7 +15799,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15821,7 +15826,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -546,7 +546,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mdr-24-869:If (52-52 &gt; 52.1-17) is not null then fixed value #completed {null}mdr-24-819:If (52-52 &gt; 52.1-17) is null then fixed value #in-progress {null}mdr-24-1555:If (52-31) is null then fixed value #in-progress {null}</t>
+mdr-24-869:If (52-52 &gt; 52.1-17) is not null then fixed value #completed {true}mdr-24-819:If (52-52 &gt; 52.1-17) is null then fixed value #in-progress {true}mdr-24-1555:If (52-31) is null then fixed value #in-progress {true}</t>
   </si>
   <si>
     <t>1555: fixed value = #in-progress when PRESCRIPTION - RELEASED DATE/TIME (52-31) if null</t>
@@ -1980,7 +1980,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mdr-24-1558:If number then source value from (52-113 &gt; 52.0113-.01) {null}</t>
+mdr-24-1558:If number then source value from (52-113 &gt; 52.0113-.01) {true}</t>
   </si>
   <si>
     <t>1558: source value based on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (52-113 &gt; 52.0113-.01) if number</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4228" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4228" uniqueCount="725">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -611,10 +611,21 @@
     <t>The category can be used to include where the medication is expected to be consumed or other types of dispenses.  Invariants can be used to bind to different value sets when profiling to bind.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/fhir/CodeSystem/medicationdispense-category"/&gt;
+    &lt;code value="outpatient"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>A code describing where the dispensed medication is expected to be consumed or administered.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationdispense-category</t>
+  </si>
+  <si>
+    <t>2215: fixed value = http://terminology.hl7.org/fhir/CodeSystem/medicationdispense-category#outpatient</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
@@ -4411,7 +4422,7 @@
         <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>81</v>
@@ -4440,7 +4451,7 @@
         <v>81</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>81</v>
+        <v>191</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>81</v>
@@ -4458,10 +4469,10 @@
         <v>115</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -4494,7 +4505,7 @@
         <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>81</v>
+        <v>194</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>81</v>
@@ -4506,7 +4517,7 @@
         <v>81</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>81</v>
@@ -4520,10 +4531,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4546,16 +4557,16 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4584,26 +4595,26 @@
         <v>181</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>91</v>
@@ -4627,30 +4638,30 @@
         <v>81</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>81</v>
@@ -4675,13 +4686,13 @@
         <v>187</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4710,10 +4721,10 @@
         <v>181</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
@@ -4731,7 +4742,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>91</v>
@@ -4755,27 +4766,27 @@
         <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4798,13 +4809,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4855,7 +4866,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4882,7 +4893,7 @@
         <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>81</v>
@@ -4896,10 +4907,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4928,7 +4939,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>140</v>
@@ -4969,19 +4980,19 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -5008,7 +5019,7 @@
         <v>81</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>81</v>
@@ -5022,10 +5033,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5048,19 +5059,19 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -5109,7 +5120,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -5136,7 +5147,7 @@
         <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>81</v>
@@ -5145,15 +5156,15 @@
         <v>81</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5176,13 +5187,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5233,7 +5244,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5260,7 +5271,7 @@
         <v>81</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>81</v>
@@ -5274,10 +5285,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5306,7 +5317,7 @@
         <v>138</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>140</v>
@@ -5347,19 +5358,19 @@
         <v>81</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -5386,7 +5397,7 @@
         <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>81</v>
@@ -5400,10 +5411,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5429,16 +5440,16 @@
         <v>105</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -5448,7 +5459,7 @@
         <v>81</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>81</v>
@@ -5487,7 +5498,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5502,7 +5513,7 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
@@ -5514,7 +5525,7 @@
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>81</v>
@@ -5523,15 +5534,15 @@
         <v>81</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5554,16 +5565,16 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5613,7 +5624,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5640,7 +5651,7 @@
         <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>81</v>
@@ -5649,15 +5660,15 @@
         <v>81</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5683,14 +5694,14 @@
         <v>111</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5739,7 +5750,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5754,19 +5765,19 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -5775,15 +5786,15 @@
         <v>81</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5806,17 +5817,17 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5865,7 +5876,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5892,7 +5903,7 @@
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>81</v>
@@ -5901,15 +5912,15 @@
         <v>81</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5932,19 +5943,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5993,7 +6004,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6020,7 +6031,7 @@
         <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>81</v>
@@ -6029,15 +6040,15 @@
         <v>81</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6060,19 +6071,19 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -6121,7 +6132,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6136,19 +6147,19 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>81</v>
@@ -6157,15 +6168,15 @@
         <v>81</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6188,16 +6199,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6247,7 +6258,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6262,36 +6273,36 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6314,13 +6325,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6371,7 +6382,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6395,10 +6406,10 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6412,10 +6423,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6438,13 +6449,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6495,7 +6506,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6522,10 +6533,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6536,10 +6547,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6562,13 +6573,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6619,7 +6630,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6643,10 +6654,10 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6660,10 +6671,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6686,13 +6697,13 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6743,7 +6754,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6770,7 +6781,7 @@
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>81</v>
@@ -6784,10 +6795,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6816,7 +6827,7 @@
         <v>138</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>140</v>
@@ -6869,7 +6880,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6896,7 +6907,7 @@
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>81</v>
@@ -6910,14 +6921,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6939,10 +6950,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -6997,7 +7008,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7038,10 +7049,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7067,14 +7078,14 @@
         <v>187</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7102,10 +7113,10 @@
         <v>181</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7123,7 +7134,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7150,7 +7161,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7164,10 +7175,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7190,13 +7201,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7247,7 +7258,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7262,7 +7273,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -7271,10 +7282,10 @@
         <v>172</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>81</v>
@@ -7288,10 +7299,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7314,13 +7325,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7371,7 +7382,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7386,7 +7397,7 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -7398,7 +7409,7 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7412,10 +7423,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7438,16 +7449,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7497,7 +7508,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7512,36 +7523,36 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7567,10 +7578,10 @@
         <v>187</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7582,7 +7593,7 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>81</v>
@@ -7600,28 +7611,28 @@
         <v>181</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7636,7 +7647,7 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -7648,24 +7659,24 @@
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7688,13 +7699,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7745,7 +7756,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7772,24 +7783,24 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7812,13 +7823,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7869,7 +7880,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7896,7 +7907,7 @@
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>81</v>
@@ -7910,10 +7921,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7942,7 +7953,7 @@
         <v>138</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>140</v>
@@ -7983,19 +7994,19 @@
         <v>81</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8022,7 +8033,7 @@
         <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>81</v>
@@ -8036,10 +8047,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8062,19 +8073,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8123,7 +8134,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8138,7 +8149,7 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
@@ -8150,7 +8161,7 @@
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -8159,15 +8170,15 @@
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8193,20 +8204,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8230,10 +8241,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8251,7 +8262,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8278,7 +8289,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8287,15 +8298,15 @@
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8318,17 +8329,17 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8377,7 +8388,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8404,7 +8415,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8413,15 +8424,15 @@
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8447,14 +8458,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8503,7 +8514,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8512,7 +8523,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8530,7 +8541,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8539,15 +8550,15 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8573,16 +8584,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8631,7 +8642,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8658,7 +8669,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8667,15 +8678,15 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8698,13 +8709,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8755,7 +8766,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8770,7 +8781,7 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
@@ -8782,7 +8793,7 @@
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>81</v>
@@ -8791,15 +8802,15 @@
         <v>81</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8822,13 +8833,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8879,7 +8890,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8894,7 +8905,7 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
@@ -8906,24 +8917,24 @@
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8946,13 +8957,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9003,7 +9014,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9027,27 +9038,27 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9070,13 +9081,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9127,7 +9138,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9154,24 +9165,24 @@
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9194,13 +9205,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9251,7 +9262,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9278,7 +9289,7 @@
         <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>81</v>
@@ -9292,10 +9303,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9324,7 +9335,7 @@
         <v>138</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>140</v>
@@ -9365,19 +9376,19 @@
         <v>81</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9404,7 +9415,7 @@
         <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>81</v>
@@ -9418,10 +9429,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9444,16 +9455,16 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9503,7 +9514,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9512,7 +9523,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9544,10 +9555,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9573,13 +9584,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9605,13 +9616,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9629,7 +9640,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9670,10 +9681,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9699,13 +9710,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9755,7 +9766,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9782,7 +9793,7 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9796,10 +9807,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9822,16 +9833,16 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9881,7 +9892,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9896,7 +9907,7 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
@@ -9922,10 +9933,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9948,13 +9959,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10005,7 +10016,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10032,13 +10043,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10046,10 +10057,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10072,13 +10083,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10129,7 +10140,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10153,10 +10164,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10165,15 +10176,15 @@
         <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10196,13 +10207,13 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10253,7 +10264,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10280,7 +10291,7 @@
         <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>81</v>
@@ -10294,10 +10305,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10326,7 +10337,7 @@
         <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>140</v>
@@ -10367,19 +10378,19 @@
         <v>81</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10406,7 +10417,7 @@
         <v>81</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>81</v>
@@ -10420,10 +10431,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10446,16 +10457,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10505,7 +10516,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10532,7 +10543,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10546,10 +10557,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10572,13 +10583,13 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10629,7 +10640,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10656,7 +10667,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10670,10 +10681,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10696,13 +10707,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10753,7 +10764,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10768,7 +10779,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10780,7 +10791,7 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10794,10 +10805,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10820,16 +10831,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10879,7 +10890,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10906,7 +10917,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10920,10 +10931,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10946,13 +10957,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11003,7 +11014,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11030,7 +11041,7 @@
         <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>81</v>
@@ -11044,10 +11055,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11076,7 +11087,7 @@
         <v>138</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>140</v>
@@ -11117,19 +11128,19 @@
         <v>81</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11156,7 +11167,7 @@
         <v>81</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>81</v>
@@ -11170,14 +11181,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11199,10 +11210,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11257,7 +11268,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11298,10 +11309,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11324,17 +11335,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11383,7 +11394,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11410,7 +11421,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11419,15 +11430,15 @@
         <v>81</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11450,17 +11461,17 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11509,7 +11520,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11524,7 +11535,7 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
@@ -11536,7 +11547,7 @@
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>81</v>
@@ -11545,15 +11556,15 @@
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11579,16 +11590,16 @@
         <v>187</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11616,10 +11627,10 @@
         <v>181</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11637,7 +11648,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11664,7 +11675,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11673,15 +11684,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11704,13 +11715,13 @@
         <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11761,7 +11772,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11776,19 +11787,19 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11797,15 +11808,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11828,19 +11839,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11889,7 +11900,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11916,7 +11927,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11930,10 +11941,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11956,16 +11967,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11994,10 +12005,10 @@
         <v>181</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12015,7 +12026,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12042,7 +12053,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12051,15 +12062,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12085,16 +12096,16 @@
         <v>187</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12122,10 +12133,10 @@
         <v>181</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12143,7 +12154,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12170,7 +12181,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12179,15 +12190,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12213,14 +12224,14 @@
         <v>187</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12248,10 +12259,10 @@
         <v>181</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12269,7 +12280,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12296,7 +12307,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12305,15 +12316,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12339,16 +12350,16 @@
         <v>187</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12376,10 +12387,10 @@
         <v>181</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12397,7 +12408,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12424,7 +12435,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12433,15 +12444,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12464,13 +12475,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12521,7 +12532,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12557,15 +12568,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12588,13 +12599,13 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12645,7 +12656,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12672,7 +12683,7 @@
         <v>81</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>81</v>
@@ -12686,10 +12697,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12718,7 +12729,7 @@
         <v>138</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>140</v>
@@ -12759,19 +12770,19 @@
         <v>81</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12798,7 +12809,7 @@
         <v>81</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>81</v>
@@ -12812,10 +12823,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12841,14 +12852,14 @@
         <v>187</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12876,10 +12887,10 @@
         <v>181</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12897,7 +12908,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12933,15 +12944,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12964,19 +12975,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13013,17 +13024,17 @@
         <v>81</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13050,7 +13061,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13059,18 +13070,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13092,19 +13103,19 @@
         <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13153,7 +13164,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13180,7 +13191,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13189,15 +13200,15 @@
         <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13220,13 +13231,13 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13277,7 +13288,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13304,7 +13315,7 @@
         <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>81</v>
@@ -13318,10 +13329,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13350,7 +13361,7 @@
         <v>138</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>140</v>
@@ -13391,19 +13402,19 @@
         <v>81</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13430,7 +13441,7 @@
         <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>81</v>
@@ -13444,10 +13455,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13470,19 +13481,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13531,7 +13542,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13543,22 +13554,22 @@
         <v>81</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>81</v>
@@ -13567,15 +13578,15 @@
         <v>81</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13601,20 +13612,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13638,10 +13649,10 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13659,7 +13670,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13686,7 +13697,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13695,15 +13706,15 @@
         <v>81</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13726,17 +13737,17 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13785,7 +13796,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13800,19 +13811,19 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>81</v>
@@ -13821,15 +13832,15 @@
         <v>81</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13855,14 +13866,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13911,7 +13922,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13920,7 +13931,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13938,7 +13949,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13947,15 +13958,15 @@
         <v>81</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13981,16 +13992,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14018,10 +14029,10 @@
         <v>167</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14039,7 +14050,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14054,19 +14065,19 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>81</v>
@@ -14075,15 +14086,15 @@
         <v>81</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14106,19 +14117,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14167,7 +14178,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14194,7 +14205,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14203,15 +14214,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14234,19 +14245,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14295,7 +14306,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14322,7 +14333,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14331,15 +14342,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14362,19 +14373,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14423,7 +14434,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14450,7 +14461,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14464,10 +14475,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14490,17 +14501,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14549,7 +14560,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14576,7 +14587,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14590,10 +14601,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14616,13 +14627,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14673,7 +14684,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14700,13 +14711,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14714,10 +14725,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14740,13 +14751,13 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14797,7 +14808,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -14824,7 +14835,7 @@
         <v>81</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>81</v>
@@ -14838,10 +14849,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14870,7 +14881,7 @@
         <v>138</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>140</v>
@@ -14923,7 +14934,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -14950,7 +14961,7 @@
         <v>81</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>81</v>
@@ -14964,14 +14975,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14993,10 +15004,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15051,7 +15062,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15092,10 +15103,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15118,13 +15129,13 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15175,7 +15186,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15202,7 +15213,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15216,10 +15227,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15245,10 +15256,10 @@
         <v>187</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15278,10 +15289,10 @@
         <v>181</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15299,7 +15310,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15326,24 +15337,24 @@
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15369,10 +15380,10 @@
         <v>187</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15402,10 +15413,10 @@
         <v>181</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15423,7 +15434,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15450,13 +15461,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15464,10 +15475,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15490,13 +15501,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15547,7 +15558,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15574,13 +15585,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15588,14 +15599,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15614,16 +15625,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15673,7 +15684,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15700,7 +15711,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15714,10 +15725,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15740,16 +15751,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15799,7 +15810,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15826,7 +15837,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseRefill.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseRefill.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
